--- a/ZGN.xlsx
+++ b/ZGN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9111B34B-6C99-4E8A-8052-AD55DB34D70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422B9E20-1377-4BEE-B074-91CC11EFCCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{E3433EC9-BF81-49D2-893F-3D58E7E5951B}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{E3433EC9-BF81-49D2-893F-3D58E7E5951B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="80">
   <si>
     <t>Ermenegildo Zegna</t>
   </si>
@@ -267,24 +267,40 @@
     <t>H225</t>
   </si>
   <si>
-    <t>Q425</t>
+    <t>H126</t>
+  </si>
+  <si>
+    <t>H226</t>
+  </si>
+  <si>
+    <t>USD/EUR</t>
+  </si>
+  <si>
+    <t>Q226</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -485,48 +501,51 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -886,8 +905,9 @@
       <c r="I2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="2">
-        <v>10.61</v>
+      <c r="J2" s="31">
+        <f>12.86*J9</f>
+        <v>11.0596</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -898,7 +918,7 @@
         <v>253.02378999999999</v>
       </c>
       <c r="K3" s="29" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -910,7 +930,7 @@
       </c>
       <c r="J4" s="25">
         <f>+J2*J3</f>
-        <v>2684.5824118999999</v>
+        <v>2798.3419078839997</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -921,11 +941,10 @@
         <v>5</v>
       </c>
       <c r="J5" s="25">
-        <f>220.121+77.432</f>
-        <v>297.553</v>
+        <v>226.715</v>
       </c>
       <c r="K5" s="29" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -933,11 +952,11 @@
         <v>6</v>
       </c>
       <c r="J6" s="25">
-        <f>162.123+84.066</f>
-        <v>246.18899999999999</v>
+        <f>96.653+128.144</f>
+        <v>224.79700000000003</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -961,7 +980,7 @@
       </c>
       <c r="J7" s="25">
         <f>+J4-J5+J6</f>
-        <v>2633.2184118999999</v>
+        <v>2796.4239078839996</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -978,6 +997,12 @@
         <v>37</v>
       </c>
       <c r="F9" s="17"/>
+      <c r="I9" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.86</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B10" s="18" t="s">
@@ -1011,7 +1036,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{460A18FB-3A62-490B-BC1A-A7EA583225D9}">
-  <dimension ref="A1:BY348"/>
+  <dimension ref="A1:CA348"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -1019,12 +1044,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:79" x14ac:dyDescent="0.2">
       <c r="C2" s="3" t="s">
         <v>42</v>
       </c>
@@ -1049,32 +1074,38 @@
       <c r="J2" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="K2" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="L2" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="U2" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:79" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>23</v>
       </c>
@@ -1088,23 +1119,27 @@
         <v>286</v>
       </c>
       <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
+      <c r="K3" s="4">
+        <v>279</v>
+      </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
-      <c r="Q3" s="4">
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4">
         <v>285</v>
       </c>
-      <c r="R3" s="4">
+      <c r="T3" s="4">
         <v>281</v>
       </c>
-      <c r="S3" s="4">
+      <c r="U3" s="4">
         <v>282</v>
       </c>
     </row>
-    <row r="4" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:79" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>24</v>
       </c>
@@ -1118,23 +1153,27 @@
         <v>120</v>
       </c>
       <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
+      <c r="K4" s="4">
+        <v>128</v>
+      </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
-      <c r="Q4" s="4">
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4">
         <v>106</v>
       </c>
-      <c r="R4" s="4">
+      <c r="T4" s="4">
         <v>116</v>
       </c>
-      <c r="S4" s="4">
+      <c r="U4" s="4">
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:79" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>25</v>
       </c>
@@ -1148,23 +1187,27 @@
         <v>66</v>
       </c>
       <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
+      <c r="K5" s="4">
+        <v>67</v>
+      </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
-      <c r="Q5" s="4">
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4">
         <v>62</v>
       </c>
-      <c r="R5" s="4">
+      <c r="T5" s="4">
         <v>64</v>
       </c>
-      <c r="S5" s="4">
+      <c r="U5" s="4">
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:79" x14ac:dyDescent="0.2">
       <c r="B6" s="6" t="s">
         <v>26</v>
       </c>
@@ -1178,24 +1221,26 @@
         <v>472</v>
       </c>
       <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
+      <c r="K6" s="7">
+        <v>474</v>
+      </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
-      <c r="Q6" s="7">
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7">
         <v>453</v>
       </c>
-      <c r="R6" s="7">
+      <c r="T6" s="7">
         <v>461</v>
       </c>
-      <c r="S6" s="7">
-        <f>+SUM(S3:S5)</f>
+      <c r="U6" s="7">
+        <f>+SUM(U3:U5)</f>
         <v>471</v>
       </c>
-      <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
       <c r="V6" s="5"/>
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
@@ -1224,8 +1269,10 @@
       <c r="AU6" s="5"/>
       <c r="AV6" s="5"/>
       <c r="AW6" s="5"/>
-    </row>
-    <row r="7" spans="1:77" x14ac:dyDescent="0.2">
+      <c r="AX6" s="5"/>
+      <c r="AY6" s="5"/>
+    </row>
+    <row r="7" spans="1:79" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>27</v>
       </c>
@@ -1243,17 +1290,17 @@
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
-      <c r="Q7" s="4">
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4">
         <v>120</v>
       </c>
-      <c r="R7" s="4">
+      <c r="T7" s="4">
         <v>118</v>
       </c>
-      <c r="S7" s="4">
+      <c r="U7" s="4">
         <v>112</v>
       </c>
-      <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
       <c r="V7" s="5"/>
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
@@ -1282,8 +1329,10 @@
       <c r="AU7" s="5"/>
       <c r="AV7" s="5"/>
       <c r="AW7" s="5"/>
-    </row>
-    <row r="8" spans="1:77" x14ac:dyDescent="0.2">
+      <c r="AX7" s="5"/>
+      <c r="AY7" s="5"/>
+    </row>
+    <row r="8" spans="1:79" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>28</v>
       </c>
@@ -1301,17 +1350,17 @@
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
-      <c r="Q8" s="4">
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4">
         <v>24</v>
       </c>
-      <c r="R8" s="4">
+      <c r="T8" s="4">
         <v>21</v>
       </c>
-      <c r="S8" s="4">
+      <c r="U8" s="4">
         <v>18</v>
       </c>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
       <c r="V8" s="5"/>
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
@@ -1340,8 +1389,10 @@
       <c r="AU8" s="5"/>
       <c r="AV8" s="5"/>
       <c r="AW8" s="5"/>
-    </row>
-    <row r="9" spans="1:77" x14ac:dyDescent="0.2">
+      <c r="AX8" s="5"/>
+      <c r="AY8" s="5"/>
+    </row>
+    <row r="9" spans="1:79" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>29</v>
       </c>
@@ -1359,17 +1410,17 @@
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
-      <c r="Q9" s="4">
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4">
         <v>67</v>
       </c>
-      <c r="R9" s="4">
+      <c r="T9" s="4">
         <v>64</v>
       </c>
-      <c r="S9" s="4">
+      <c r="U9" s="4">
         <v>65</v>
       </c>
-      <c r="T9" s="25"/>
-      <c r="U9" s="25"/>
       <c r="V9" s="25"/>
       <c r="W9" s="25"/>
       <c r="X9" s="25"/>
@@ -1426,8 +1477,10 @@
       <c r="BW9" s="25"/>
       <c r="BX9" s="25"/>
       <c r="BY9" s="25"/>
-    </row>
-    <row r="10" spans="1:77" x14ac:dyDescent="0.2">
+      <c r="BZ9" s="25"/>
+      <c r="CA9" s="25"/>
+    </row>
+    <row r="10" spans="1:79" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>30</v>
       </c>
@@ -1445,18 +1498,18 @@
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
-      <c r="Q10" s="4">
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4">
         <v>211</v>
       </c>
-      <c r="R10" s="4">
+      <c r="T10" s="4">
         <v>203</v>
       </c>
-      <c r="S10" s="4">
-        <f>+SUM(S7:S9)</f>
+      <c r="U10" s="4">
+        <f>+SUM(U7:U9)</f>
         <v>195</v>
       </c>
-      <c r="T10" s="25"/>
-      <c r="U10" s="25"/>
       <c r="V10" s="25"/>
       <c r="W10" s="25"/>
       <c r="X10" s="25"/>
@@ -1513,8 +1566,10 @@
       <c r="BW10" s="25"/>
       <c r="BX10" s="25"/>
       <c r="BY10" s="25"/>
-    </row>
-    <row r="11" spans="1:77" x14ac:dyDescent="0.2">
+      <c r="BZ10" s="25"/>
+      <c r="CA10" s="25"/>
+    </row>
+    <row r="11" spans="1:79" x14ac:dyDescent="0.2">
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
@@ -1590,8 +1645,10 @@
       <c r="BW11" s="25"/>
       <c r="BX11" s="25"/>
       <c r="BY11" s="25"/>
-    </row>
-    <row r="12" spans="1:77" x14ac:dyDescent="0.2">
+      <c r="BZ11" s="25"/>
+      <c r="CA11" s="25"/>
+    </row>
+    <row r="12" spans="1:79" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>17</v>
       </c>
@@ -1601,40 +1658,42 @@
         <v>541.31899999999996</v>
       </c>
       <c r="F12" s="25">
-        <f>+Q12-E12</f>
+        <f>+S12-E12</f>
         <v>568.17200000000003</v>
       </c>
       <c r="G12" s="25">
         <v>566.06700000000001</v>
       </c>
       <c r="H12" s="25">
-        <f>+R12-G12</f>
+        <f>+T12-G12</f>
         <v>597.65499999999997</v>
       </c>
       <c r="I12" s="25">
         <v>570.40899999999999</v>
       </c>
       <c r="J12" s="25">
-        <f>+S12-I12</f>
+        <f t="shared" ref="J12:J18" si="0">+U12-I12</f>
         <v>611.17400000000009</v>
       </c>
-      <c r="K12" s="25"/>
+      <c r="K12" s="25">
+        <v>724.26499999999999</v>
+      </c>
       <c r="L12" s="25"/>
       <c r="M12" s="25"/>
       <c r="N12" s="25"/>
       <c r="O12" s="25"/>
       <c r="P12" s="25"/>
-      <c r="Q12" s="25">
+      <c r="Q12" s="25"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25">
         <v>1109.491</v>
       </c>
-      <c r="R12" s="25">
+      <c r="T12" s="25">
         <v>1163.722</v>
       </c>
-      <c r="S12" s="25">
+      <c r="U12" s="25">
         <v>1181.5830000000001</v>
       </c>
-      <c r="T12" s="25"/>
-      <c r="U12" s="25"/>
       <c r="V12" s="25"/>
       <c r="W12" s="25"/>
       <c r="X12" s="25"/>
@@ -1691,8 +1750,10 @@
       <c r="BW12" s="25"/>
       <c r="BX12" s="25"/>
       <c r="BY12" s="25"/>
-    </row>
-    <row r="13" spans="1:77" x14ac:dyDescent="0.2">
+      <c r="BZ12" s="25"/>
+      <c r="CA12" s="25"/>
+    </row>
+    <row r="13" spans="1:79" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
@@ -1702,40 +1763,42 @@
         <v>206.95099999999999</v>
       </c>
       <c r="F13" s="25">
-        <f t="shared" ref="F13:F17" si="0">+Q13-E13</f>
+        <f t="shared" ref="F13:F17" si="1">+S13-E13</f>
         <v>171.45900000000003</v>
       </c>
       <c r="G13" s="25">
         <v>166.721</v>
       </c>
       <c r="H13" s="25">
-        <f t="shared" ref="H13:H30" si="1">+R13-G13</f>
+        <f t="shared" ref="H13:H30" si="2">+T13-G13</f>
         <v>147.99099999999999</v>
       </c>
       <c r="I13" s="25">
         <v>129.154</v>
       </c>
       <c r="J13" s="25">
-        <f>+S13-I13</f>
+        <f t="shared" si="0"/>
         <v>139.315</v>
       </c>
-      <c r="K13" s="25"/>
+      <c r="K13" s="32">
+        <v>123.10599999999999</v>
+      </c>
       <c r="L13" s="25"/>
       <c r="M13" s="25"/>
       <c r="N13" s="25"/>
       <c r="O13" s="25"/>
       <c r="P13" s="25"/>
-      <c r="Q13" s="25">
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25">
         <v>378.41</v>
       </c>
-      <c r="R13" s="25">
+      <c r="T13" s="25">
         <v>314.71199999999999</v>
       </c>
-      <c r="S13" s="25">
+      <c r="U13" s="25">
         <v>268.46899999999999</v>
       </c>
-      <c r="T13" s="25"/>
-      <c r="U13" s="25"/>
       <c r="V13" s="25"/>
       <c r="W13" s="25"/>
       <c r="X13" s="25"/>
@@ -1792,8 +1855,10 @@
       <c r="BW13" s="25"/>
       <c r="BX13" s="25"/>
       <c r="BY13" s="25"/>
-    </row>
-    <row r="14" spans="1:77" x14ac:dyDescent="0.2">
+      <c r="BZ13" s="25"/>
+      <c r="CA13" s="25"/>
+    </row>
+    <row r="14" spans="1:79" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>19</v>
       </c>
@@ -1803,40 +1868,42 @@
         <v>64.015000000000001</v>
       </c>
       <c r="F14" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>171.51600000000002</v>
       </c>
       <c r="G14" s="25">
         <v>148.49299999999999</v>
       </c>
       <c r="H14" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>166.02100000000002</v>
       </c>
       <c r="I14" s="25">
         <v>152.715</v>
       </c>
       <c r="J14" s="25">
-        <f>+S14-I14</f>
+        <f t="shared" si="0"/>
         <v>164.34099999999998</v>
       </c>
-      <c r="K14" s="25"/>
+      <c r="K14" s="25">
+        <v>156.81700000000001</v>
+      </c>
       <c r="L14" s="25"/>
       <c r="M14" s="25"/>
       <c r="N14" s="25"/>
       <c r="O14" s="25"/>
       <c r="P14" s="25"/>
-      <c r="Q14" s="25">
+      <c r="Q14" s="25"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25">
         <v>235.53100000000001</v>
       </c>
-      <c r="R14" s="25">
+      <c r="T14" s="25">
         <v>314.51400000000001</v>
       </c>
-      <c r="S14" s="25">
+      <c r="U14" s="25">
         <v>317.05599999999998</v>
       </c>
-      <c r="T14" s="25"/>
-      <c r="U14" s="25"/>
       <c r="V14" s="25"/>
       <c r="W14" s="25"/>
       <c r="X14" s="25"/>
@@ -1893,8 +1960,10 @@
       <c r="BW14" s="25"/>
       <c r="BX14" s="25"/>
       <c r="BY14" s="25"/>
-    </row>
-    <row r="15" spans="1:77" x14ac:dyDescent="0.2">
+      <c r="BZ14" s="25"/>
+      <c r="CA14" s="25"/>
+    </row>
+    <row r="15" spans="1:79" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>21</v>
       </c>
@@ -1904,40 +1973,42 @@
         <v>73.072000000000003</v>
       </c>
       <c r="F15" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>77.913999999999987</v>
       </c>
       <c r="G15" s="25">
         <v>71.835999999999999</v>
       </c>
       <c r="H15" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>66.316999999999993</v>
       </c>
       <c r="I15" s="25">
         <v>67.061000000000007</v>
       </c>
       <c r="J15" s="25">
-        <f>+S15-I15</f>
+        <f t="shared" si="0"/>
         <v>67.168000000000006</v>
       </c>
-      <c r="K15" s="25"/>
+      <c r="K15" s="25">
+        <v>67.012</v>
+      </c>
       <c r="L15" s="25"/>
       <c r="M15" s="25"/>
       <c r="N15" s="25"/>
       <c r="O15" s="25"/>
       <c r="P15" s="25"/>
-      <c r="Q15" s="25">
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25">
         <v>150.98599999999999</v>
       </c>
-      <c r="R15" s="25">
+      <c r="T15" s="25">
         <v>138.15299999999999</v>
       </c>
-      <c r="S15" s="25">
+      <c r="U15" s="25">
         <v>134.22900000000001</v>
       </c>
-      <c r="T15" s="25"/>
-      <c r="U15" s="25"/>
       <c r="V15" s="25"/>
       <c r="W15" s="25"/>
       <c r="X15" s="25"/>
@@ -1994,8 +2065,10 @@
       <c r="BW15" s="25"/>
       <c r="BX15" s="25"/>
       <c r="BY15" s="25"/>
-    </row>
-    <row r="16" spans="1:77" x14ac:dyDescent="0.2">
+      <c r="BZ15" s="25"/>
+      <c r="CA15" s="25"/>
+    </row>
+    <row r="16" spans="1:79" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>22</v>
       </c>
@@ -2005,40 +2078,42 @@
         <v>17.702000000000002</v>
       </c>
       <c r="F16" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12.428999999999998</v>
       </c>
       <c r="G16" s="25">
         <v>7.0049999999999999</v>
       </c>
       <c r="H16" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.5410000000000004</v>
       </c>
       <c r="I16" s="25">
         <v>8.3510000000000009</v>
       </c>
       <c r="J16" s="25">
-        <f>+S16-I16</f>
+        <f t="shared" si="0"/>
         <v>7.2589999999999986</v>
       </c>
-      <c r="K16" s="25"/>
+      <c r="K16" s="25">
+        <v>5.782</v>
+      </c>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
       <c r="N16" s="25"/>
       <c r="O16" s="25"/>
       <c r="P16" s="25"/>
-      <c r="Q16" s="25">
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="25">
         <v>30.131</v>
       </c>
-      <c r="R16" s="25">
+      <c r="T16" s="25">
         <v>15.545999999999999</v>
       </c>
-      <c r="S16" s="25">
+      <c r="U16" s="25">
         <v>15.61</v>
       </c>
-      <c r="T16" s="25"/>
-      <c r="U16" s="25"/>
       <c r="V16" s="25"/>
       <c r="W16" s="25"/>
       <c r="X16" s="25"/>
@@ -2095,8 +2170,10 @@
       <c r="BW16" s="25"/>
       <c r="BX16" s="25"/>
       <c r="BY16" s="25"/>
-    </row>
-    <row r="17" spans="2:77" x14ac:dyDescent="0.2">
+      <c r="BZ16" s="25"/>
+      <c r="CA16" s="25"/>
+    </row>
+    <row r="17" spans="2:79" x14ac:dyDescent="0.2">
       <c r="B17" s="6" t="s">
         <v>20</v>
       </c>
@@ -2106,57 +2183,59 @@
         <v>903.05899999999997</v>
       </c>
       <c r="F17" s="26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1001.4900000000002</v>
       </c>
       <c r="G17" s="26">
         <v>960.11199999999997</v>
       </c>
       <c r="H17" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>986.53499999999997</v>
       </c>
       <c r="I17" s="26">
         <v>927.69</v>
       </c>
       <c r="J17" s="26">
-        <f>+S17-I17</f>
+        <f t="shared" si="0"/>
         <v>989.25699999999983</v>
       </c>
-      <c r="K17" s="25"/>
-      <c r="L17" s="26">
-        <f t="shared" ref="L17:Q17" si="2">+SUM(L12:L16)</f>
+      <c r="K17" s="26">
+        <v>987.29</v>
+      </c>
+      <c r="L17" s="26"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="26">
+        <f t="shared" ref="N17:S17" si="3">+SUM(N12:N16)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="26">
-        <f t="shared" si="2"/>
+      <c r="O17" s="26">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N17" s="26">
-        <f t="shared" si="2"/>
+      <c r="P17" s="26">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O17" s="26">
-        <f t="shared" si="2"/>
+      <c r="Q17" s="26">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P17" s="26">
-        <f t="shared" si="2"/>
+      <c r="R17" s="26">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="26">
-        <f t="shared" si="2"/>
+      <c r="S17" s="26">
+        <f t="shared" si="3"/>
         <v>1904.5490000000002</v>
       </c>
-      <c r="R17" s="26">
-        <f>+SUM(R12:R16)</f>
+      <c r="T17" s="26">
+        <f>+SUM(T12:T16)</f>
         <v>1946.6469999999999</v>
       </c>
-      <c r="S17" s="26">
+      <c r="U17" s="26">
         <v>1916.9469999999999</v>
       </c>
-      <c r="T17" s="25"/>
-      <c r="U17" s="25"/>
       <c r="V17" s="25"/>
       <c r="W17" s="25"/>
       <c r="X17" s="25"/>
@@ -2213,8 +2292,10 @@
       <c r="BW17" s="25"/>
       <c r="BX17" s="25"/>
       <c r="BY17" s="25"/>
-    </row>
-    <row r="18" spans="2:77" x14ac:dyDescent="0.2">
+      <c r="BZ17" s="25"/>
+      <c r="CA17" s="25"/>
+    </row>
+    <row r="18" spans="2:79" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>48</v>
       </c>
@@ -2228,31 +2309,33 @@
         <v>322.678</v>
       </c>
       <c r="H18" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>327.40899999999999</v>
       </c>
       <c r="I18" s="25">
         <v>301.65800000000002</v>
       </c>
       <c r="J18" s="25">
-        <f>+S18-I18</f>
+        <f t="shared" si="0"/>
         <v>321.25199999999995</v>
       </c>
-      <c r="K18" s="25"/>
+      <c r="K18" s="25">
+        <v>319.47500000000002</v>
+      </c>
       <c r="L18" s="25"/>
       <c r="M18" s="25"/>
       <c r="N18" s="25"/>
       <c r="O18" s="25"/>
       <c r="P18" s="25"/>
       <c r="Q18" s="25"/>
-      <c r="R18" s="28">
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="28">
         <v>650.08699999999999</v>
       </c>
-      <c r="S18" s="25">
+      <c r="U18" s="25">
         <v>622.91</v>
       </c>
-      <c r="T18" s="25"/>
-      <c r="U18" s="25"/>
       <c r="V18" s="25"/>
       <c r="W18" s="25"/>
       <c r="X18" s="25"/>
@@ -2309,25 +2392,27 @@
       <c r="BW18" s="25"/>
       <c r="BX18" s="25"/>
       <c r="BY18" s="25"/>
-    </row>
-    <row r="19" spans="2:77" x14ac:dyDescent="0.2">
+      <c r="BZ18" s="25"/>
+      <c r="CA18" s="25"/>
+    </row>
+    <row r="19" spans="2:79" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="25">
-        <f t="shared" ref="C19:F19" si="3">+C17-C18</f>
+        <f t="shared" ref="C19:F19" si="4">+C17-C18</f>
         <v>0</v>
       </c>
       <c r="D19" s="25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E19" s="25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>579.8309999999999</v>
       </c>
       <c r="F19" s="25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1001.4900000000002</v>
       </c>
       <c r="G19" s="25">
@@ -2335,40 +2420,43 @@
         <v>637.43399999999997</v>
       </c>
       <c r="H19" s="25">
-        <f t="shared" ref="H19:J19" si="4">+H17-H18</f>
+        <f t="shared" ref="H19:K19" si="5">+H17-H18</f>
         <v>659.12599999999998</v>
       </c>
       <c r="I19" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>626.03200000000004</v>
       </c>
       <c r="J19" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>668.00499999999988</v>
       </c>
-      <c r="K19" s="25"/>
+      <c r="K19" s="25">
+        <f t="shared" si="5"/>
+        <v>667.81499999999994</v>
+      </c>
       <c r="L19" s="25"/>
       <c r="M19" s="25"/>
       <c r="N19" s="25"/>
       <c r="O19" s="25"/>
-      <c r="P19" s="25">
-        <f t="shared" ref="P19:R19" si="5">+P17-P18</f>
+      <c r="P19" s="25"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="25">
+        <f t="shared" ref="R19:T19" si="6">+R17-R18</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="25">
-        <f t="shared" si="5"/>
+      <c r="S19" s="25">
+        <f t="shared" si="6"/>
         <v>1904.5490000000002</v>
       </c>
-      <c r="R19" s="25">
-        <f t="shared" si="5"/>
+      <c r="T19" s="25">
+        <f t="shared" si="6"/>
         <v>1296.56</v>
       </c>
-      <c r="S19" s="25">
-        <f>+S17-S18</f>
+      <c r="U19" s="25">
+        <f>+U17-U18</f>
         <v>1294.0369999999998</v>
       </c>
-      <c r="T19" s="25"/>
-      <c r="U19" s="25"/>
       <c r="V19" s="25"/>
       <c r="W19" s="25"/>
       <c r="X19" s="25"/>
@@ -2425,8 +2513,10 @@
       <c r="BW19" s="25"/>
       <c r="BX19" s="25"/>
       <c r="BY19" s="25"/>
-    </row>
-    <row r="20" spans="2:77" x14ac:dyDescent="0.2">
+      <c r="BZ19" s="25"/>
+      <c r="CA19" s="25"/>
+    </row>
+    <row r="20" spans="2:79" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>50</v>
       </c>
@@ -2440,31 +2530,33 @@
         <v>497.61200000000002</v>
       </c>
       <c r="H20" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>510.71199999999993</v>
       </c>
       <c r="I20" s="25">
         <v>501.80399999999997</v>
       </c>
       <c r="J20" s="25">
-        <f>+S20-I20</f>
+        <f>+U20-I20</f>
         <v>532.06700000000012</v>
       </c>
-      <c r="K20" s="25"/>
+      <c r="K20" s="25">
+        <v>531.07100000000003</v>
+      </c>
       <c r="L20" s="25"/>
       <c r="M20" s="25"/>
       <c r="N20" s="25"/>
       <c r="O20" s="25"/>
       <c r="P20" s="25"/>
       <c r="Q20" s="25"/>
-      <c r="R20" s="25">
+      <c r="R20" s="25"/>
+      <c r="S20" s="25"/>
+      <c r="T20" s="25">
         <v>1008.324</v>
       </c>
-      <c r="S20" s="25">
+      <c r="U20" s="25">
         <v>1033.8710000000001</v>
       </c>
-      <c r="T20" s="25"/>
-      <c r="U20" s="25"/>
       <c r="V20" s="25"/>
       <c r="W20" s="25"/>
       <c r="X20" s="25"/>
@@ -2521,8 +2613,10 @@
       <c r="BW20" s="25"/>
       <c r="BX20" s="25"/>
       <c r="BY20" s="25"/>
-    </row>
-    <row r="21" spans="2:77" x14ac:dyDescent="0.2">
+      <c r="BZ20" s="25"/>
+      <c r="CA20" s="25"/>
+    </row>
+    <row r="21" spans="2:79" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>51</v>
       </c>
@@ -2536,31 +2630,33 @@
         <v>66.751000000000005</v>
       </c>
       <c r="H21" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>54.632999999999996</v>
       </c>
       <c r="I21" s="25">
         <v>62.881999999999998</v>
       </c>
       <c r="J21" s="25">
-        <f>+S21-I21</f>
+        <f>+U21-I21</f>
         <v>57.804000000000009</v>
       </c>
-      <c r="K21" s="25"/>
+      <c r="K21" s="25">
+        <v>68.204999999999998</v>
+      </c>
       <c r="L21" s="25"/>
       <c r="M21" s="25"/>
       <c r="N21" s="25"/>
       <c r="O21" s="25"/>
       <c r="P21" s="25"/>
       <c r="Q21" s="25"/>
-      <c r="R21" s="25">
+      <c r="R21" s="25"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="25">
         <v>121.384</v>
       </c>
-      <c r="S21" s="25">
+      <c r="U21" s="25">
         <v>120.68600000000001</v>
       </c>
-      <c r="T21" s="25"/>
-      <c r="U21" s="25"/>
       <c r="V21" s="25"/>
       <c r="W21" s="25"/>
       <c r="X21" s="25"/>
@@ -2617,25 +2713,27 @@
       <c r="BW21" s="25"/>
       <c r="BX21" s="25"/>
       <c r="BY21" s="25"/>
-    </row>
-    <row r="22" spans="2:77" x14ac:dyDescent="0.2">
+      <c r="BZ21" s="25"/>
+      <c r="CA21" s="25"/>
+    </row>
+    <row r="22" spans="2:79" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C22" s="25">
-        <f t="shared" ref="C22:F22" si="6">+C19-C20-C21</f>
+        <f t="shared" ref="C22:F22" si="7">+C19-C20-C21</f>
         <v>0</v>
       </c>
       <c r="D22" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E22" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>116.50899999999993</v>
       </c>
       <c r="F22" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1001.4900000000002</v>
       </c>
       <c r="G22" s="25">
@@ -2643,37 +2741,40 @@
         <v>73.070999999999941</v>
       </c>
       <c r="H22" s="25">
-        <f t="shared" ref="H22:J22" si="7">+H19-H20-H21</f>
+        <f t="shared" ref="H22:K22" si="8">+H19-H20-H21</f>
         <v>93.781000000000049</v>
       </c>
       <c r="I22" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>61.346000000000068</v>
       </c>
       <c r="J22" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>78.133999999999759</v>
       </c>
-      <c r="K22" s="25"/>
+      <c r="K22" s="25">
+        <f t="shared" si="8"/>
+        <v>68.538999999999916</v>
+      </c>
       <c r="L22" s="25"/>
       <c r="M22" s="25"/>
       <c r="N22" s="25"/>
       <c r="O22" s="25"/>
       <c r="P22" s="25"/>
-      <c r="Q22" s="25">
-        <f>+Q19-Q20-Q21</f>
-        <v>1904.5490000000002</v>
-      </c>
-      <c r="R22" s="25">
-        <f>+R19-R20-R21</f>
-        <v>166.85199999999998</v>
-      </c>
+      <c r="Q22" s="25"/>
+      <c r="R22" s="25"/>
       <c r="S22" s="25">
         <f>+S19-S20-S21</f>
+        <v>1904.5490000000002</v>
+      </c>
+      <c r="T22" s="25">
+        <f>+T19-T20-T21</f>
+        <v>166.85199999999998</v>
+      </c>
+      <c r="U22" s="25">
+        <f>+U19-U20-U21</f>
         <v>139.47999999999971</v>
       </c>
-      <c r="T22" s="25"/>
-      <c r="U22" s="25"/>
       <c r="V22" s="25"/>
       <c r="W22" s="25"/>
       <c r="X22" s="25"/>
@@ -2730,8 +2831,10 @@
       <c r="BW22" s="25"/>
       <c r="BX22" s="25"/>
       <c r="BY22" s="25"/>
-    </row>
-    <row r="23" spans="2:77" x14ac:dyDescent="0.2">
+      <c r="BZ22" s="25"/>
+      <c r="CA22" s="25"/>
+    </row>
+    <row r="23" spans="2:79" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>53</v>
       </c>
@@ -2745,31 +2848,33 @@
         <v>12.106</v>
       </c>
       <c r="H23" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13.921999999999999</v>
       </c>
       <c r="I23" s="25">
         <v>21.207000000000001</v>
       </c>
       <c r="J23" s="25">
-        <f>+S23-I23</f>
+        <f>+U23-I23</f>
         <v>20.302</v>
       </c>
-      <c r="K23" s="25"/>
+      <c r="K23" s="25">
+        <v>9.3729999999999993</v>
+      </c>
       <c r="L23" s="25"/>
       <c r="M23" s="25"/>
       <c r="N23" s="25"/>
       <c r="O23" s="25"/>
       <c r="P23" s="25"/>
       <c r="Q23" s="25"/>
-      <c r="R23" s="25">
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="25">
         <v>26.027999999999999</v>
       </c>
-      <c r="S23" s="25">
+      <c r="U23" s="25">
         <v>41.509</v>
       </c>
-      <c r="T23" s="25"/>
-      <c r="U23" s="25"/>
       <c r="V23" s="25"/>
       <c r="W23" s="25"/>
       <c r="X23" s="25"/>
@@ -2826,8 +2931,10 @@
       <c r="BW23" s="25"/>
       <c r="BX23" s="25"/>
       <c r="BY23" s="25"/>
-    </row>
-    <row r="24" spans="2:77" x14ac:dyDescent="0.2">
+      <c r="BZ23" s="25"/>
+      <c r="CA23" s="25"/>
+    </row>
+    <row r="24" spans="2:79" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>54</v>
       </c>
@@ -2841,31 +2948,33 @@
         <v>29.266999999999999</v>
       </c>
       <c r="H24" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>22.727999999999998</v>
       </c>
       <c r="I24" s="25">
         <v>25.408000000000001</v>
       </c>
       <c r="J24" s="25">
-        <f>+S24-I24</f>
+        <f>+U24-I24</f>
         <v>25.062999999999995</v>
       </c>
-      <c r="K24" s="25"/>
+      <c r="K24" s="25">
+        <v>28.989000000000001</v>
+      </c>
       <c r="L24" s="25"/>
       <c r="M24" s="25"/>
       <c r="N24" s="25"/>
       <c r="O24" s="25"/>
       <c r="P24" s="25"/>
       <c r="Q24" s="25"/>
-      <c r="R24" s="25">
+      <c r="R24" s="25"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="25">
         <v>51.994999999999997</v>
       </c>
-      <c r="S24" s="25">
+      <c r="U24" s="25">
         <v>50.470999999999997</v>
       </c>
-      <c r="T24" s="25"/>
-      <c r="U24" s="25"/>
       <c r="V24" s="25"/>
       <c r="W24" s="25"/>
       <c r="X24" s="25"/>
@@ -2922,8 +3031,10 @@
       <c r="BW24" s="25"/>
       <c r="BX24" s="25"/>
       <c r="BY24" s="25"/>
-    </row>
-    <row r="25" spans="2:77" x14ac:dyDescent="0.2">
+      <c r="BZ24" s="25"/>
+      <c r="CA24" s="25"/>
+    </row>
+    <row r="25" spans="2:79" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>55</v>
       </c>
@@ -2937,31 +3048,33 @@
         <v>7.6840000000000002</v>
       </c>
       <c r="H25" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.653999999999999</v>
       </c>
       <c r="I25" s="25">
         <v>-10.214</v>
       </c>
       <c r="J25" s="25">
-        <f>+S25-I25</f>
+        <f>+U25-I25</f>
         <v>1.2140000000000004</v>
       </c>
-      <c r="K25" s="25"/>
+      <c r="K25" s="25">
+        <v>3.0819999999999999</v>
+      </c>
       <c r="L25" s="25"/>
       <c r="M25" s="25"/>
       <c r="N25" s="25"/>
       <c r="O25" s="25"/>
       <c r="P25" s="25"/>
       <c r="Q25" s="25"/>
-      <c r="R25" s="25">
+      <c r="R25" s="25"/>
+      <c r="S25" s="25"/>
+      <c r="T25" s="25">
         <v>11.337999999999999</v>
       </c>
-      <c r="S25" s="25">
+      <c r="U25" s="25">
         <v>-9</v>
       </c>
-      <c r="T25" s="25"/>
-      <c r="U25" s="25"/>
       <c r="V25" s="25"/>
       <c r="W25" s="25"/>
       <c r="X25" s="25"/>
@@ -3018,8 +3131,10 @@
       <c r="BW25" s="25"/>
       <c r="BX25" s="25"/>
       <c r="BY25" s="25"/>
-    </row>
-    <row r="26" spans="2:77" x14ac:dyDescent="0.2">
+      <c r="BZ25" s="25"/>
+      <c r="CA25" s="25"/>
+    </row>
+    <row r="26" spans="2:79" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>56</v>
       </c>
@@ -3033,31 +3148,33 @@
         <v>0.314</v>
       </c>
       <c r="H26" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.74699999999999989</v>
       </c>
       <c r="I26" s="25">
         <v>0.65900000000000003</v>
       </c>
       <c r="J26" s="25">
-        <f>+S26-I26</f>
+        <f>+U26-I26</f>
         <v>-0.13500000000000001</v>
       </c>
-      <c r="K26" s="25"/>
+      <c r="K26" s="25">
+        <v>0.64400000000000002</v>
+      </c>
       <c r="L26" s="25"/>
       <c r="M26" s="25"/>
       <c r="N26" s="25"/>
       <c r="O26" s="25"/>
       <c r="P26" s="25"/>
       <c r="Q26" s="25"/>
-      <c r="R26" s="25">
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="25">
         <v>1.0609999999999999</v>
       </c>
-      <c r="S26" s="25">
+      <c r="U26" s="25">
         <v>0.52400000000000002</v>
       </c>
-      <c r="T26" s="25"/>
-      <c r="U26" s="25"/>
       <c r="V26" s="25"/>
       <c r="W26" s="25"/>
       <c r="X26" s="25"/>
@@ -3114,25 +3231,27 @@
       <c r="BW26" s="25"/>
       <c r="BX26" s="25"/>
       <c r="BY26" s="25"/>
-    </row>
-    <row r="27" spans="2:77" x14ac:dyDescent="0.2">
+      <c r="BZ26" s="25"/>
+      <c r="CA26" s="25"/>
+    </row>
+    <row r="27" spans="2:79" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C27" s="25">
-        <f t="shared" ref="C27:F27" si="8">+C22+C23-C24-C25+C26</f>
+        <f t="shared" ref="C27:F27" si="9">+C22+C23-C24-C25+C26</f>
         <v>0</v>
       </c>
       <c r="D27" s="25">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E27" s="25">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>78.277999999999935</v>
       </c>
       <c r="F27" s="25">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1001.4900000000002</v>
       </c>
       <c r="G27" s="25">
@@ -3140,52 +3259,55 @@
         <v>48.539999999999942</v>
       </c>
       <c r="H27" s="25">
-        <f t="shared" ref="H27:J27" si="9">+H22+H23-H24-H25+H26</f>
+        <f t="shared" ref="H27:K27" si="10">+H22+H23-H24-H25+H26</f>
         <v>82.068000000000055</v>
       </c>
       <c r="I27" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>68.018000000000072</v>
       </c>
       <c r="J27" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>72.023999999999759</v>
       </c>
-      <c r="K27" s="25"/>
-      <c r="L27" s="25">
-        <f t="shared" ref="L27:S27" si="10">+L22+L23-L24-L25+L26</f>
+      <c r="K27" s="25">
+        <f t="shared" si="10"/>
+        <v>46.484999999999914</v>
+      </c>
+      <c r="L27" s="25"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="25">
+        <f t="shared" ref="N27:U27" si="11">+N22+N23-N24-N25+N26</f>
         <v>0</v>
       </c>
-      <c r="M27" s="25">
-        <f t="shared" si="10"/>
+      <c r="O27" s="25">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="N27" s="25">
-        <f t="shared" si="10"/>
+      <c r="P27" s="25">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="O27" s="25">
-        <f t="shared" si="10"/>
+      <c r="Q27" s="25">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P27" s="25">
-        <f t="shared" si="10"/>
+      <c r="R27" s="25">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="25">
-        <f t="shared" si="10"/>
+      <c r="S27" s="25">
+        <f t="shared" si="11"/>
         <v>1904.5490000000002</v>
       </c>
-      <c r="R27" s="25">
-        <f t="shared" si="10"/>
+      <c r="T27" s="25">
+        <f t="shared" si="11"/>
         <v>130.60799999999998</v>
       </c>
-      <c r="S27" s="25">
-        <f t="shared" si="10"/>
+      <c r="U27" s="25">
+        <f t="shared" si="11"/>
         <v>140.04199999999969</v>
       </c>
-      <c r="T27" s="25"/>
-      <c r="U27" s="25"/>
       <c r="V27" s="25"/>
       <c r="W27" s="25"/>
       <c r="X27" s="25"/>
@@ -3242,8 +3364,10 @@
       <c r="BW27" s="25"/>
       <c r="BX27" s="25"/>
       <c r="BY27" s="25"/>
-    </row>
-    <row r="28" spans="2:77" x14ac:dyDescent="0.2">
+      <c r="BZ27" s="25"/>
+      <c r="CA27" s="25"/>
+    </row>
+    <row r="28" spans="2:79" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>58</v>
       </c>
@@ -3257,31 +3381,33 @@
         <v>17.218</v>
       </c>
       <c r="H28" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>22.529</v>
       </c>
       <c r="I28" s="25">
         <v>20.116</v>
       </c>
       <c r="J28" s="25">
-        <f>+S28-I28</f>
+        <f>+U28-I28</f>
         <v>10.439</v>
       </c>
-      <c r="K28" s="25"/>
+      <c r="K28" s="25">
+        <v>18.052</v>
+      </c>
       <c r="L28" s="25"/>
       <c r="M28" s="25"/>
       <c r="N28" s="25"/>
       <c r="O28" s="25"/>
       <c r="P28" s="25"/>
       <c r="Q28" s="25"/>
-      <c r="R28" s="25">
+      <c r="R28" s="25"/>
+      <c r="S28" s="25"/>
+      <c r="T28" s="25">
         <v>39.747</v>
       </c>
-      <c r="S28" s="25">
+      <c r="U28" s="25">
         <v>30.555</v>
       </c>
-      <c r="T28" s="25"/>
-      <c r="U28" s="25"/>
       <c r="V28" s="25"/>
       <c r="W28" s="25"/>
       <c r="X28" s="25"/>
@@ -3338,25 +3464,27 @@
       <c r="BW28" s="25"/>
       <c r="BX28" s="25"/>
       <c r="BY28" s="25"/>
-    </row>
-    <row r="29" spans="2:77" x14ac:dyDescent="0.2">
+      <c r="BZ28" s="25"/>
+      <c r="CA28" s="25"/>
+    </row>
+    <row r="29" spans="2:79" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C29" s="25">
-        <f t="shared" ref="C29:F29" si="11">+C27-C28</f>
+        <f t="shared" ref="C29:F29" si="12">+C27-C28</f>
         <v>0</v>
       </c>
       <c r="D29" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E29" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>52.115999999999936</v>
       </c>
       <c r="F29" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1001.4900000000002</v>
       </c>
       <c r="G29" s="25">
@@ -3364,37 +3492,40 @@
         <v>31.321999999999942</v>
       </c>
       <c r="H29" s="25">
-        <f t="shared" ref="H29:J29" si="12">+H27-H28</f>
+        <f t="shared" ref="H29:K29" si="13">+H27-H28</f>
         <v>59.539000000000058</v>
       </c>
       <c r="I29" s="25">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>47.902000000000072</v>
       </c>
       <c r="J29" s="25">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>61.584999999999759</v>
       </c>
-      <c r="K29" s="25"/>
+      <c r="K29" s="25">
+        <f t="shared" si="13"/>
+        <v>28.432999999999915</v>
+      </c>
       <c r="L29" s="25"/>
       <c r="M29" s="25"/>
       <c r="N29" s="25"/>
       <c r="O29" s="25"/>
       <c r="P29" s="25"/>
-      <c r="Q29" s="25">
-        <f>+Q27-Q28</f>
-        <v>1904.5490000000002</v>
-      </c>
-      <c r="R29" s="25">
-        <f>+R27-R28</f>
-        <v>90.860999999999976</v>
-      </c>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="25"/>
       <c r="S29" s="25">
         <f>+S27-S28</f>
+        <v>1904.5490000000002</v>
+      </c>
+      <c r="T29" s="25">
+        <f>+T27-T28</f>
+        <v>90.860999999999976</v>
+      </c>
+      <c r="U29" s="25">
+        <f>+U27-U28</f>
         <v>109.48699999999968</v>
       </c>
-      <c r="T29" s="25"/>
-      <c r="U29" s="25"/>
       <c r="V29" s="25"/>
       <c r="W29" s="25"/>
       <c r="X29" s="25"/>
@@ -3451,8 +3582,10 @@
       <c r="BW29" s="25"/>
       <c r="BX29" s="25"/>
       <c r="BY29" s="25"/>
-    </row>
-    <row r="30" spans="2:77" x14ac:dyDescent="0.2">
+      <c r="BZ29" s="25"/>
+      <c r="CA29" s="25"/>
+    </row>
+    <row r="30" spans="2:79" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>60</v>
       </c>
@@ -3466,31 +3599,33 @@
         <v>6.2469999999999999</v>
       </c>
       <c r="H30" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.5310000000000006</v>
       </c>
       <c r="I30" s="25">
         <v>4.819</v>
       </c>
       <c r="J30" s="25">
-        <f>+S30-I30</f>
+        <f>+U30-I30</f>
         <v>6.0859999999999994</v>
       </c>
-      <c r="K30" s="25"/>
+      <c r="K30" s="25">
+        <v>5.2709999999999999</v>
+      </c>
       <c r="L30" s="25"/>
       <c r="M30" s="25"/>
       <c r="N30" s="25"/>
       <c r="O30" s="25"/>
       <c r="P30" s="25"/>
       <c r="Q30" s="25"/>
-      <c r="R30" s="25">
+      <c r="R30" s="25"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="25">
         <v>13.778</v>
       </c>
-      <c r="S30" s="25">
+      <c r="U30" s="25">
         <v>10.904999999999999</v>
       </c>
-      <c r="T30" s="25"/>
-      <c r="U30" s="25"/>
       <c r="V30" s="25"/>
       <c r="W30" s="25"/>
       <c r="X30" s="25"/>
@@ -3547,25 +3682,27 @@
       <c r="BW30" s="25"/>
       <c r="BX30" s="25"/>
       <c r="BY30" s="25"/>
-    </row>
-    <row r="31" spans="2:77" x14ac:dyDescent="0.2">
+      <c r="BZ30" s="25"/>
+      <c r="CA30" s="25"/>
+    </row>
+    <row r="31" spans="2:79" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C31" s="25">
-        <f t="shared" ref="C31:F31" si="13">+C29-C30</f>
+        <f t="shared" ref="C31:F31" si="14">+C29-C30</f>
         <v>0</v>
       </c>
       <c r="D31" s="25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E31" s="25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>45.966999999999935</v>
       </c>
       <c r="F31" s="25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1001.4900000000002</v>
       </c>
       <c r="G31" s="25">
@@ -3573,43 +3710,46 @@
         <v>25.074999999999942</v>
       </c>
       <c r="H31" s="25">
-        <f t="shared" ref="H31:J31" si="14">+H29-H30</f>
+        <f t="shared" ref="H31:K31" si="15">+H29-H30</f>
         <v>52.00800000000006</v>
       </c>
       <c r="I31" s="25">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>43.083000000000069</v>
       </c>
       <c r="J31" s="25">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>55.498999999999761</v>
       </c>
-      <c r="K31" s="25"/>
+      <c r="K31" s="25">
+        <f t="shared" si="15"/>
+        <v>23.161999999999914</v>
+      </c>
       <c r="L31" s="25"/>
       <c r="M31" s="25"/>
       <c r="N31" s="25"/>
-      <c r="O31" s="28">
-        <f t="shared" ref="O31:R31" si="15">+O29-O30</f>
+      <c r="O31" s="25"/>
+      <c r="P31" s="25"/>
+      <c r="Q31" s="28">
+        <f t="shared" ref="Q31:T31" si="16">+Q29-Q30</f>
         <v>0</v>
       </c>
-      <c r="P31" s="28">
-        <f t="shared" si="15"/>
+      <c r="R31" s="28">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q31" s="28">
-        <f t="shared" si="15"/>
+      <c r="S31" s="28">
+        <f t="shared" si="16"/>
         <v>1904.5490000000002</v>
       </c>
-      <c r="R31" s="28">
-        <f t="shared" si="15"/>
+      <c r="T31" s="28">
+        <f t="shared" si="16"/>
         <v>77.08299999999997</v>
       </c>
-      <c r="S31" s="28">
-        <f>+S29-S30</f>
+      <c r="U31" s="28">
+        <f>+U29-U30</f>
         <v>98.581999999999681</v>
       </c>
-      <c r="T31" s="25"/>
-      <c r="U31" s="25"/>
       <c r="V31" s="25"/>
       <c r="W31" s="25"/>
       <c r="X31" s="25"/>
@@ -3666,8 +3806,10 @@
       <c r="BW31" s="25"/>
       <c r="BX31" s="25"/>
       <c r="BY31" s="25"/>
-    </row>
-    <row r="32" spans="2:77" x14ac:dyDescent="0.2">
+      <c r="BZ31" s="25"/>
+      <c r="CA31" s="25"/>
+    </row>
+    <row r="32" spans="2:79" x14ac:dyDescent="0.2">
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
@@ -3715,33 +3857,35 @@
       <c r="AU32" s="5"/>
       <c r="AV32" s="5"/>
       <c r="AW32" s="5"/>
-    </row>
-    <row r="33" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX32" s="5"/>
+      <c r="AY32" s="5"/>
+    </row>
+    <row r="33" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C33" s="24" t="e">
-        <f t="shared" ref="C33:H33" si="16">+C31/C34</f>
+        <f t="shared" ref="C33:H33" si="17">+C31/C34</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D33" s="24" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E33" s="24" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F33" s="24" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G33" s="24">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.10004765739736834</v>
       </c>
       <c r="H33" s="24">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.20750861678653443</v>
       </c>
       <c r="I33" s="24">
@@ -3752,23 +3896,26 @@
         <f>+J31/J34</f>
         <v>0.21934301118483665</v>
       </c>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
+      <c r="K33" s="24">
+        <f>+K31/K34</f>
+        <v>9.1540799384911262E-2</v>
+      </c>
+      <c r="L33" s="24"/>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
       <c r="P33" s="5"/>
       <c r="Q33" s="5"/>
-      <c r="R33" s="5">
-        <f>+R31/R34</f>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5">
+        <f>+T31/T34</f>
         <v>0.30755627418390263</v>
       </c>
-      <c r="S33" s="5">
-        <f>+S31/S34</f>
+      <c r="U33" s="5">
+        <f>+U31/U34</f>
         <v>0.38961553773263646</v>
       </c>
-      <c r="T33" s="5"/>
-      <c r="U33" s="5"/>
       <c r="V33" s="5"/>
       <c r="W33" s="5"/>
       <c r="X33" s="5"/>
@@ -3797,8 +3944,10 @@
       <c r="AU33" s="5"/>
       <c r="AV33" s="5"/>
       <c r="AW33" s="5"/>
-    </row>
-    <row r="34" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX33" s="5"/>
+      <c r="AY33" s="5"/>
+    </row>
+    <row r="34" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>3</v>
       </c>
@@ -3818,21 +3967,23 @@
       <c r="J34" s="5">
         <v>253.02378999999999</v>
       </c>
-      <c r="K34" s="5"/>
+      <c r="K34" s="5">
+        <v>253.02378999999999</v>
+      </c>
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
-      <c r="R34" s="5">
+      <c r="R34" s="5"/>
+      <c r="S34" s="5"/>
+      <c r="T34" s="5">
         <v>250.63055600000001</v>
       </c>
-      <c r="S34" s="5">
+      <c r="U34" s="5">
         <v>253.02378999999999</v>
       </c>
-      <c r="T34" s="5"/>
-      <c r="U34" s="5"/>
       <c r="V34" s="5"/>
       <c r="W34" s="5"/>
       <c r="X34" s="5"/>
@@ -3861,8 +4012,10 @@
       <c r="AU34" s="5"/>
       <c r="AV34" s="5"/>
       <c r="AW34" s="5"/>
-    </row>
-    <row r="35" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX34" s="5"/>
+      <c r="AY34" s="5"/>
+    </row>
+    <row r="35" spans="2:51" x14ac:dyDescent="0.2">
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -3910,8 +4063,10 @@
       <c r="AU35" s="5"/>
       <c r="AV35" s="5"/>
       <c r="AW35" s="5"/>
-    </row>
-    <row r="36" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX35" s="5"/>
+      <c r="AY35" s="5"/>
+    </row>
+    <row r="36" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
         <v>62</v>
       </c>
@@ -3924,27 +4079,24 @@
         <v>4.5717959280941578E-2</v>
       </c>
       <c r="H36" s="9">
-        <f t="shared" ref="H36:J41" si="17">+H12/F12-1</f>
+        <f t="shared" ref="H36:K41" si="18">+H12/F12-1</f>
         <v>5.1890976676076894E-2</v>
       </c>
       <c r="I36" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>7.6704701033623035E-3</v>
       </c>
       <c r="J36" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.2620073453748502E-2</v>
       </c>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="9" t="e">
-        <f t="shared" ref="M36:N36" si="18">+M12/L12-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N36" s="9" t="e">
+      <c r="K36" s="9">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
+        <v>0.26972926444007728</v>
+      </c>
+      <c r="L36" s="9"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
       <c r="O36" s="9" t="e">
         <f t="shared" ref="O36:P36" si="19">+O12/N12-1</f>
         <v>#DIV/0!</v>
@@ -3954,19 +4106,25 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q36" s="9" t="e">
-        <f t="shared" ref="Q36:S40" si="20">+Q12/P12-1</f>
+        <f t="shared" ref="Q36:R36" si="20">+Q12/P12-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R36" s="9">
+      <c r="R36" s="9" t="e">
         <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S36" s="9" t="e">
+        <f t="shared" ref="S36:U40" si="21">+S12/R12-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T36" s="9">
+        <f t="shared" si="21"/>
         <v>4.8879170718825193E-2</v>
       </c>
-      <c r="S36" s="9">
-        <f t="shared" si="20"/>
+      <c r="U36" s="9">
+        <f t="shared" si="21"/>
         <v>1.5348167345809571E-2</v>
       </c>
-      <c r="T36" s="5"/>
-      <c r="U36" s="5"/>
       <c r="V36" s="5"/>
       <c r="W36" s="5"/>
       <c r="X36" s="5"/>
@@ -3995,8 +4153,10 @@
       <c r="AU36" s="5"/>
       <c r="AV36" s="5"/>
       <c r="AW36" s="5"/>
-    </row>
-    <row r="37" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX36" s="5"/>
+      <c r="AY36" s="5"/>
+    </row>
+    <row r="37" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
         <v>63</v>
       </c>
@@ -4005,31 +4165,28 @@
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="9">
-        <f t="shared" ref="G37:G41" si="21">+G13/E13-1</f>
+        <f t="shared" ref="G37:G41" si="22">+G13/E13-1</f>
         <v>-0.19439384202057486</v>
       </c>
       <c r="H37" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-0.13687237182066869</v>
       </c>
       <c r="I37" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-0.22532854289501625</v>
       </c>
       <c r="J37" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-5.8625186666756646E-2</v>
       </c>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="9" t="e">
-        <f t="shared" ref="M37:N37" si="22">+M13/L13-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N37" s="9" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="K37" s="9">
+        <f t="shared" si="18"/>
+        <v>-4.6827817953760675E-2</v>
+      </c>
+      <c r="L37" s="9"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
       <c r="O37" s="9" t="e">
         <f t="shared" ref="O37:P37" si="23">+O13/N13-1</f>
         <v>#DIV/0!</v>
@@ -4039,19 +4196,25 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q37" s="9" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="Q37:R37" si="24">+Q13/P13-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R37" s="9">
-        <f t="shared" si="20"/>
+      <c r="R37" s="9" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S37" s="9" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T37" s="9">
+        <f t="shared" si="21"/>
         <v>-0.16833064665310127</v>
       </c>
-      <c r="S37" s="9">
-        <f t="shared" si="20"/>
+      <c r="U37" s="9">
+        <f t="shared" si="21"/>
         <v>-0.1469375174762958</v>
       </c>
-      <c r="T37" s="5"/>
-      <c r="U37" s="5"/>
       <c r="V37" s="5"/>
       <c r="W37" s="5"/>
       <c r="X37" s="5"/>
@@ -4080,8 +4243,10 @@
       <c r="AU37" s="5"/>
       <c r="AV37" s="5"/>
       <c r="AW37" s="5"/>
-    </row>
-    <row r="38" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX37" s="5"/>
+      <c r="AY37" s="5"/>
+    </row>
+    <row r="38" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
         <v>64</v>
       </c>
@@ -4090,31 +4255,28 @@
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1.3196594548152776</v>
       </c>
       <c r="H38" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-3.2037827374705619E-2</v>
       </c>
       <c r="I38" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.8432316674860125E-2</v>
       </c>
       <c r="J38" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-1.0119201787725851E-2</v>
       </c>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="9" t="e">
-        <f t="shared" ref="M38:N38" si="24">+M14/L14-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N38" s="9" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="K38" s="9">
+        <f t="shared" si="18"/>
+        <v>2.6860491765707373E-2</v>
+      </c>
+      <c r="L38" s="9"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
       <c r="O38" s="9" t="e">
         <f t="shared" ref="O38:P38" si="25">+O14/N14-1</f>
         <v>#DIV/0!</v>
@@ -4124,19 +4286,25 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q38" s="9" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="Q38:R38" si="26">+Q14/P14-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R38" s="9">
-        <f t="shared" si="20"/>
+      <c r="R38" s="9" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S38" s="9" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T38" s="9">
+        <f t="shared" si="21"/>
         <v>0.33534014630770481</v>
       </c>
-      <c r="S38" s="9">
-        <f t="shared" si="20"/>
+      <c r="U38" s="9">
+        <f t="shared" si="21"/>
         <v>8.0823111212855459E-3</v>
       </c>
-      <c r="T38" s="5"/>
-      <c r="U38" s="5"/>
       <c r="V38" s="5"/>
       <c r="W38" s="5"/>
       <c r="X38" s="5"/>
@@ -4165,8 +4333,10 @@
       <c r="AU38" s="5"/>
       <c r="AV38" s="5"/>
       <c r="AW38" s="5"/>
-    </row>
-    <row r="39" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX38" s="5"/>
+      <c r="AY38" s="5"/>
+    </row>
+    <row r="39" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
         <v>65</v>
       </c>
@@ -4175,31 +4345,28 @@
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-1.69148237354938E-2</v>
       </c>
       <c r="H39" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-0.14884359678620007</v>
       </c>
       <c r="I39" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-6.6470850270059501E-2</v>
       </c>
       <c r="J39" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1.2832305442043612E-2</v>
       </c>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="9" t="e">
-        <f t="shared" ref="M39:N39" si="26">+M15/L15-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N39" s="9" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="K39" s="9">
+        <f t="shared" si="18"/>
+        <v>-7.3067803939708131E-4</v>
+      </c>
+      <c r="L39" s="9"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
       <c r="O39" s="9" t="e">
         <f t="shared" ref="O39:P39" si="27">+O15/N15-1</f>
         <v>#DIV/0!</v>
@@ -4209,19 +4376,25 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q39" s="9" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="Q39:R39" si="28">+Q15/P15-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R39" s="9">
-        <f t="shared" si="20"/>
+      <c r="R39" s="9" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S39" s="9" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T39" s="9">
+        <f t="shared" si="21"/>
         <v>-8.4994635264196705E-2</v>
       </c>
-      <c r="S39" s="9">
-        <f t="shared" si="20"/>
+      <c r="U39" s="9">
+        <f t="shared" si="21"/>
         <v>-2.8403292002345037E-2</v>
       </c>
-      <c r="T39" s="5"/>
-      <c r="U39" s="5"/>
       <c r="V39" s="5"/>
       <c r="W39" s="5"/>
       <c r="X39" s="5"/>
@@ -4250,8 +4423,10 @@
       <c r="AU39" s="5"/>
       <c r="AV39" s="5"/>
       <c r="AW39" s="5"/>
-    </row>
-    <row r="40" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX39" s="5"/>
+      <c r="AY39" s="5"/>
+    </row>
+    <row r="40" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
         <v>66</v>
       </c>
@@ -4260,31 +4435,28 @@
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-0.60428200203366855</v>
       </c>
       <c r="H40" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-0.3128167994207095</v>
       </c>
       <c r="I40" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.19214846538187014</v>
       </c>
       <c r="J40" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-0.1500995199625339</v>
       </c>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="9" t="e">
-        <f t="shared" ref="M40:N40" si="28">+M16/L16-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N40" s="9" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="K40" s="9">
+        <f t="shared" si="18"/>
+        <v>-0.30762782900251473</v>
+      </c>
+      <c r="L40" s="9"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
       <c r="O40" s="9" t="e">
         <f t="shared" ref="O40:P40" si="29">+O16/N16-1</f>
         <v>#DIV/0!</v>
@@ -4294,19 +4466,25 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q40" s="9" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="Q40:R40" si="30">+Q16/P16-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R40" s="9">
-        <f t="shared" si="20"/>
+      <c r="R40" s="9" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S40" s="9" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T40" s="9">
+        <f t="shared" si="21"/>
         <v>-0.48405296870332881</v>
       </c>
-      <c r="S40" s="9">
-        <f t="shared" si="20"/>
+      <c r="U40" s="9">
+        <f t="shared" si="21"/>
         <v>4.1168146146919327E-3</v>
       </c>
-      <c r="T40" s="5"/>
-      <c r="U40" s="5"/>
       <c r="V40" s="5"/>
       <c r="W40" s="5"/>
       <c r="X40" s="5"/>
@@ -4335,8 +4513,10 @@
       <c r="AU40" s="5"/>
       <c r="AV40" s="5"/>
       <c r="AW40" s="5"/>
-    </row>
-    <row r="41" spans="2:49" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AX40" s="5"/>
+      <c r="AY40" s="5"/>
+    </row>
+    <row r="41" spans="2:51" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B41" s="6" t="s">
         <v>67</v>
       </c>
@@ -4345,31 +4525,28 @@
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
       <c r="G41" s="27">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>6.31774889569785E-2</v>
       </c>
       <c r="H41" s="27">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-1.4932750202198974E-2</v>
       </c>
       <c r="I41" s="27">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-3.3768976952688767E-2</v>
       </c>
       <c r="J41" s="27">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.7591519814298415E-3</v>
       </c>
-      <c r="K41" s="8"/>
-      <c r="L41" s="8"/>
-      <c r="M41" s="27" t="e">
-        <f t="shared" ref="M41:N41" si="30">+M17/L17-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N41" s="27" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="K41" s="27">
+        <f t="shared" si="18"/>
+        <v>6.4245599284243449E-2</v>
+      </c>
+      <c r="L41" s="27"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
       <c r="O41" s="27" t="e">
         <f t="shared" ref="O41:P41" si="31">+O17/N17-1</f>
         <v>#DIV/0!</v>
@@ -4379,19 +4556,25 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q41" s="27" t="e">
-        <f>+Q17/P17-1</f>
+        <f t="shared" ref="Q41:R41" si="32">+Q17/P17-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R41" s="27">
-        <f t="shared" ref="R41:S41" si="32">+R17/Q17-1</f>
+      <c r="R41" s="27" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S41" s="27" t="e">
+        <f>+S17/R17-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T41" s="27">
+        <f t="shared" ref="T41:U41" si="33">+T17/S17-1</f>
         <v>2.2103920665732302E-2</v>
       </c>
-      <c r="S41" s="27">
-        <f t="shared" si="32"/>
+      <c r="U41" s="27">
+        <f t="shared" si="33"/>
         <v>-1.525700345260339E-2</v>
       </c>
-      <c r="T41" s="8"/>
-      <c r="U41" s="8"/>
       <c r="V41" s="8"/>
       <c r="W41" s="8"/>
       <c r="X41" s="8"/>
@@ -4420,25 +4603,27 @@
       <c r="AU41" s="8"/>
       <c r="AV41" s="8"/>
       <c r="AW41" s="8"/>
-    </row>
-    <row r="42" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX41" s="8"/>
+      <c r="AY41" s="8"/>
+    </row>
+    <row r="42" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C42" s="9" t="e">
-        <f t="shared" ref="C42:F42" si="33">+C19/C17</f>
+        <f t="shared" ref="C42:F42" si="34">+C19/C17</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D42" s="9" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E42" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.64207432736952952</v>
       </c>
       <c r="F42" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G42" s="9">
@@ -4446,52 +4631,55 @@
         <v>0.66391629309913847</v>
       </c>
       <c r="H42" s="9">
-        <f t="shared" ref="H42:I42" si="34">+H19/H17</f>
+        <f t="shared" ref="H42:I42" si="35">+H19/H17</f>
         <v>0.66812226631594418</v>
       </c>
       <c r="I42" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.67482887602539643</v>
       </c>
       <c r="J42" s="9">
-        <f t="shared" ref="J42" si="35">+J19/J17</f>
+        <f t="shared" ref="J42:K42" si="36">+J19/J17</f>
         <v>0.67525931077566292</v>
       </c>
-      <c r="K42" s="5"/>
-      <c r="L42" s="9" t="e">
-        <f t="shared" ref="L42:S42" si="36">+L19/L17</f>
+      <c r="K42" s="9">
+        <f t="shared" si="36"/>
+        <v>0.67641219904992456</v>
+      </c>
+      <c r="L42" s="9"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="9" t="e">
+        <f t="shared" ref="N42:U42" si="37">+N19/N17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M42" s="9" t="e">
-        <f t="shared" ref="M42:N42" si="37">+M19/M17</f>
+      <c r="O42" s="9" t="e">
+        <f t="shared" ref="O42:P42" si="38">+O19/O17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N42" s="9" t="e">
+      <c r="P42" s="9" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q42" s="9" t="e">
         <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O42" s="9" t="e">
-        <f t="shared" si="36"/>
+      <c r="R42" s="9" t="e">
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P42" s="9" t="e">
-        <f t="shared" si="36"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q42" s="9">
-        <f t="shared" si="36"/>
+      <c r="S42" s="9">
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
-      <c r="R42" s="9">
-        <f t="shared" si="36"/>
+      <c r="T42" s="9">
+        <f t="shared" si="37"/>
         <v>0.66604782479822999</v>
       </c>
-      <c r="S42" s="9">
-        <f t="shared" si="36"/>
+      <c r="U42" s="9">
+        <f t="shared" si="37"/>
         <v>0.67505100558335718</v>
       </c>
-      <c r="T42" s="5"/>
-      <c r="U42" s="5"/>
       <c r="V42" s="5"/>
       <c r="W42" s="5"/>
       <c r="X42" s="5"/>
@@ -4520,25 +4708,27 @@
       <c r="AU42" s="5"/>
       <c r="AV42" s="5"/>
       <c r="AW42" s="5"/>
-    </row>
-    <row r="43" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX42" s="5"/>
+      <c r="AY42" s="5"/>
+    </row>
+    <row r="43" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C43" s="9" t="e">
-        <f t="shared" ref="C43:F43" si="38">+C22/C17</f>
+        <f t="shared" ref="C43:F43" si="39">+C22/C17</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D43" s="9" t="e">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E43" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.12901593362116975</v>
       </c>
       <c r="F43" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1</v>
       </c>
       <c r="G43" s="9">
@@ -4546,52 +4736,55 @@
         <v>7.6106745879647317E-2</v>
       </c>
       <c r="H43" s="9">
-        <f t="shared" ref="H43:I43" si="39">+H22/H17</f>
+        <f t="shared" ref="H43:I43" si="40">+H22/H17</f>
         <v>9.5060996315386739E-2</v>
       </c>
       <c r="I43" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>6.612769351830898E-2</v>
       </c>
       <c r="J43" s="9">
-        <f t="shared" ref="J43" si="40">+J22/J17</f>
+        <f t="shared" ref="J43:K43" si="41">+J22/J17</f>
         <v>7.898250909520961E-2</v>
       </c>
-      <c r="K43" s="5"/>
-      <c r="L43" s="9" t="e">
-        <f t="shared" ref="L43:S43" si="41">+L22/L17</f>
+      <c r="K43" s="9">
+        <f t="shared" si="41"/>
+        <v>6.9421345298746995E-2</v>
+      </c>
+      <c r="L43" s="9"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="9" t="e">
+        <f t="shared" ref="N43:U43" si="42">+N22/N17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M43" s="9" t="e">
-        <f t="shared" ref="M43:N43" si="42">+M22/M17</f>
+      <c r="O43" s="9" t="e">
+        <f t="shared" ref="O43:P43" si="43">+O22/O17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N43" s="9" t="e">
+      <c r="P43" s="9" t="e">
+        <f t="shared" si="43"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q43" s="9" t="e">
         <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O43" s="9" t="e">
-        <f t="shared" si="41"/>
+      <c r="R43" s="9" t="e">
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P43" s="9" t="e">
-        <f t="shared" si="41"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q43" s="9">
-        <f t="shared" si="41"/>
+      <c r="S43" s="9">
+        <f t="shared" si="42"/>
         <v>1</v>
       </c>
-      <c r="R43" s="9">
-        <f t="shared" si="41"/>
+      <c r="T43" s="9">
+        <f t="shared" si="42"/>
         <v>8.5712509766793871E-2</v>
       </c>
-      <c r="S43" s="9">
-        <f t="shared" si="41"/>
+      <c r="U43" s="9">
+        <f t="shared" si="42"/>
         <v>7.2761531748138944E-2</v>
       </c>
-      <c r="T43" s="5"/>
-      <c r="U43" s="5"/>
       <c r="V43" s="5"/>
       <c r="W43" s="5"/>
       <c r="X43" s="5"/>
@@ -4620,25 +4813,27 @@
       <c r="AU43" s="5"/>
       <c r="AV43" s="5"/>
       <c r="AW43" s="5"/>
-    </row>
-    <row r="44" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX43" s="5"/>
+      <c r="AY43" s="5"/>
+    </row>
+    <row r="44" spans="2:51" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C44" s="9" t="e">
-        <f t="shared" ref="C44:F44" si="43">+C30/C29</f>
+        <f t="shared" ref="C44:F44" si="44">+C30/C29</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D44" s="9" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E44" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.11798679867986814</v>
       </c>
       <c r="F44" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="G44" s="9">
@@ -4646,52 +4841,55 @@
         <v>0.19944447991826866</v>
       </c>
       <c r="H44" s="9">
-        <f t="shared" ref="H44:I44" si="44">+H30/H29</f>
+        <f t="shared" ref="H44:I44" si="45">+H30/H29</f>
         <v>0.1264885201296628</v>
       </c>
       <c r="I44" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.10060122750615826</v>
       </c>
       <c r="J44" s="9">
-        <f t="shared" ref="J44" si="45">+J30/J29</f>
+        <f t="shared" ref="J44:K44" si="46">+J30/J29</f>
         <v>9.8822765283754541E-2</v>
       </c>
-      <c r="K44" s="5"/>
-      <c r="L44" s="9" t="e">
-        <f t="shared" ref="L44:S44" si="46">+L30/L29</f>
+      <c r="K44" s="9">
+        <f t="shared" si="46"/>
+        <v>0.185383181514438</v>
+      </c>
+      <c r="L44" s="9"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="9" t="e">
+        <f t="shared" ref="N44:U44" si="47">+N30/N29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M44" s="9" t="e">
-        <f t="shared" ref="M44:N44" si="47">+M30/M29</f>
+      <c r="O44" s="9" t="e">
+        <f t="shared" ref="O44:P44" si="48">+O30/O29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N44" s="9" t="e">
+      <c r="P44" s="9" t="e">
+        <f t="shared" si="48"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q44" s="9" t="e">
         <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O44" s="9" t="e">
-        <f t="shared" si="46"/>
+      <c r="R44" s="9" t="e">
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P44" s="9" t="e">
-        <f t="shared" si="46"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q44" s="9">
-        <f t="shared" si="46"/>
+      <c r="S44" s="9">
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
-      <c r="R44" s="9">
-        <f t="shared" si="46"/>
+      <c r="T44" s="9">
+        <f t="shared" si="47"/>
         <v>0.15163821661659022</v>
       </c>
-      <c r="S44" s="9">
-        <f t="shared" si="46"/>
+      <c r="U44" s="9">
+        <f t="shared" si="47"/>
         <v>9.9600865856220661E-2</v>
       </c>
-      <c r="T44" s="5"/>
-      <c r="U44" s="5"/>
       <c r="V44" s="5"/>
       <c r="W44" s="5"/>
       <c r="X44" s="5"/>
@@ -4720,8 +4918,10 @@
       <c r="AU44" s="5"/>
       <c r="AV44" s="5"/>
       <c r="AW44" s="5"/>
-    </row>
-    <row r="45" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX44" s="5"/>
+      <c r="AY44" s="5"/>
+    </row>
+    <row r="45" spans="2:51" x14ac:dyDescent="0.2">
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
@@ -4769,8 +4969,10 @@
       <c r="AU45" s="5"/>
       <c r="AV45" s="5"/>
       <c r="AW45" s="5"/>
-    </row>
-    <row r="46" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX45" s="5"/>
+      <c r="AY45" s="5"/>
+    </row>
+    <row r="46" spans="2:51" x14ac:dyDescent="0.2">
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
@@ -4818,8 +5020,10 @@
       <c r="AU46" s="5"/>
       <c r="AV46" s="5"/>
       <c r="AW46" s="5"/>
-    </row>
-    <row r="47" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX46" s="5"/>
+      <c r="AY46" s="5"/>
+    </row>
+    <row r="47" spans="2:51" x14ac:dyDescent="0.2">
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
@@ -4867,8 +5071,10 @@
       <c r="AU47" s="5"/>
       <c r="AV47" s="5"/>
       <c r="AW47" s="5"/>
-    </row>
-    <row r="48" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX47" s="5"/>
+      <c r="AY47" s="5"/>
+    </row>
+    <row r="48" spans="2:51" x14ac:dyDescent="0.2">
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
@@ -4916,8 +5122,10 @@
       <c r="AU48" s="5"/>
       <c r="AV48" s="5"/>
       <c r="AW48" s="5"/>
-    </row>
-    <row r="49" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX48" s="5"/>
+      <c r="AY48" s="5"/>
+    </row>
+    <row r="49" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
@@ -4965,8 +5173,10 @@
       <c r="AU49" s="5"/>
       <c r="AV49" s="5"/>
       <c r="AW49" s="5"/>
-    </row>
-    <row r="50" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX49" s="5"/>
+      <c r="AY49" s="5"/>
+    </row>
+    <row r="50" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
@@ -5014,8 +5224,10 @@
       <c r="AU50" s="5"/>
       <c r="AV50" s="5"/>
       <c r="AW50" s="5"/>
-    </row>
-    <row r="51" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX50" s="5"/>
+      <c r="AY50" s="5"/>
+    </row>
+    <row r="51" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
@@ -5063,8 +5275,10 @@
       <c r="AU51" s="5"/>
       <c r="AV51" s="5"/>
       <c r="AW51" s="5"/>
-    </row>
-    <row r="52" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX51" s="5"/>
+      <c r="AY51" s="5"/>
+    </row>
+    <row r="52" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
@@ -5112,8 +5326,10 @@
       <c r="AU52" s="5"/>
       <c r="AV52" s="5"/>
       <c r="AW52" s="5"/>
-    </row>
-    <row r="53" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX52" s="5"/>
+      <c r="AY52" s="5"/>
+    </row>
+    <row r="53" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
@@ -5161,8 +5377,10 @@
       <c r="AU53" s="5"/>
       <c r="AV53" s="5"/>
       <c r="AW53" s="5"/>
-    </row>
-    <row r="54" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX53" s="5"/>
+      <c r="AY53" s="5"/>
+    </row>
+    <row r="54" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
@@ -5210,8 +5428,10 @@
       <c r="AU54" s="5"/>
       <c r="AV54" s="5"/>
       <c r="AW54" s="5"/>
-    </row>
-    <row r="55" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX54" s="5"/>
+      <c r="AY54" s="5"/>
+    </row>
+    <row r="55" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
@@ -5259,8 +5479,10 @@
       <c r="AU55" s="5"/>
       <c r="AV55" s="5"/>
       <c r="AW55" s="5"/>
-    </row>
-    <row r="56" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX55" s="5"/>
+      <c r="AY55" s="5"/>
+    </row>
+    <row r="56" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
@@ -5308,8 +5530,10 @@
       <c r="AU56" s="5"/>
       <c r="AV56" s="5"/>
       <c r="AW56" s="5"/>
-    </row>
-    <row r="57" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX56" s="5"/>
+      <c r="AY56" s="5"/>
+    </row>
+    <row r="57" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
@@ -5357,8 +5581,10 @@
       <c r="AU57" s="5"/>
       <c r="AV57" s="5"/>
       <c r="AW57" s="5"/>
-    </row>
-    <row r="58" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX57" s="5"/>
+      <c r="AY57" s="5"/>
+    </row>
+    <row r="58" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
@@ -5406,8 +5632,10 @@
       <c r="AU58" s="5"/>
       <c r="AV58" s="5"/>
       <c r="AW58" s="5"/>
-    </row>
-    <row r="59" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX58" s="5"/>
+      <c r="AY58" s="5"/>
+    </row>
+    <row r="59" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
@@ -5455,8 +5683,10 @@
       <c r="AU59" s="5"/>
       <c r="AV59" s="5"/>
       <c r="AW59" s="5"/>
-    </row>
-    <row r="60" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX59" s="5"/>
+      <c r="AY59" s="5"/>
+    </row>
+    <row r="60" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
@@ -5504,8 +5734,10 @@
       <c r="AU60" s="5"/>
       <c r="AV60" s="5"/>
       <c r="AW60" s="5"/>
-    </row>
-    <row r="61" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX60" s="5"/>
+      <c r="AY60" s="5"/>
+    </row>
+    <row r="61" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
@@ -5553,8 +5785,10 @@
       <c r="AU61" s="5"/>
       <c r="AV61" s="5"/>
       <c r="AW61" s="5"/>
-    </row>
-    <row r="62" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX61" s="5"/>
+      <c r="AY61" s="5"/>
+    </row>
+    <row r="62" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
@@ -5602,8 +5836,10 @@
       <c r="AU62" s="5"/>
       <c r="AV62" s="5"/>
       <c r="AW62" s="5"/>
-    </row>
-    <row r="63" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX62" s="5"/>
+      <c r="AY62" s="5"/>
+    </row>
+    <row r="63" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
@@ -5651,8 +5887,10 @@
       <c r="AU63" s="5"/>
       <c r="AV63" s="5"/>
       <c r="AW63" s="5"/>
-    </row>
-    <row r="64" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX63" s="5"/>
+      <c r="AY63" s="5"/>
+    </row>
+    <row r="64" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
@@ -5700,8 +5938,10 @@
       <c r="AU64" s="5"/>
       <c r="AV64" s="5"/>
       <c r="AW64" s="5"/>
-    </row>
-    <row r="65" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX64" s="5"/>
+      <c r="AY64" s="5"/>
+    </row>
+    <row r="65" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
@@ -5749,8 +5989,10 @@
       <c r="AU65" s="5"/>
       <c r="AV65" s="5"/>
       <c r="AW65" s="5"/>
-    </row>
-    <row r="66" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX65" s="5"/>
+      <c r="AY65" s="5"/>
+    </row>
+    <row r="66" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
       <c r="E66" s="5"/>
@@ -5798,8 +6040,10 @@
       <c r="AU66" s="5"/>
       <c r="AV66" s="5"/>
       <c r="AW66" s="5"/>
-    </row>
-    <row r="67" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX66" s="5"/>
+      <c r="AY66" s="5"/>
+    </row>
+    <row r="67" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
@@ -5847,8 +6091,10 @@
       <c r="AU67" s="5"/>
       <c r="AV67" s="5"/>
       <c r="AW67" s="5"/>
-    </row>
-    <row r="68" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX67" s="5"/>
+      <c r="AY67" s="5"/>
+    </row>
+    <row r="68" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
       <c r="E68" s="5"/>
@@ -5896,8 +6142,10 @@
       <c r="AU68" s="5"/>
       <c r="AV68" s="5"/>
       <c r="AW68" s="5"/>
-    </row>
-    <row r="69" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX68" s="5"/>
+      <c r="AY68" s="5"/>
+    </row>
+    <row r="69" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C69" s="5"/>
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
@@ -5945,8 +6193,10 @@
       <c r="AU69" s="5"/>
       <c r="AV69" s="5"/>
       <c r="AW69" s="5"/>
-    </row>
-    <row r="70" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX69" s="5"/>
+      <c r="AY69" s="5"/>
+    </row>
+    <row r="70" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C70" s="5"/>
       <c r="D70" s="5"/>
       <c r="E70" s="5"/>
@@ -5994,8 +6244,10 @@
       <c r="AU70" s="5"/>
       <c r="AV70" s="5"/>
       <c r="AW70" s="5"/>
-    </row>
-    <row r="71" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX70" s="5"/>
+      <c r="AY70" s="5"/>
+    </row>
+    <row r="71" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
       <c r="E71" s="5"/>
@@ -6043,8 +6295,10 @@
       <c r="AU71" s="5"/>
       <c r="AV71" s="5"/>
       <c r="AW71" s="5"/>
-    </row>
-    <row r="72" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX71" s="5"/>
+      <c r="AY71" s="5"/>
+    </row>
+    <row r="72" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C72" s="5"/>
       <c r="D72" s="5"/>
       <c r="E72" s="5"/>
@@ -6092,8 +6346,10 @@
       <c r="AU72" s="5"/>
       <c r="AV72" s="5"/>
       <c r="AW72" s="5"/>
-    </row>
-    <row r="73" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX72" s="5"/>
+      <c r="AY72" s="5"/>
+    </row>
+    <row r="73" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
@@ -6141,8 +6397,10 @@
       <c r="AU73" s="5"/>
       <c r="AV73" s="5"/>
       <c r="AW73" s="5"/>
-    </row>
-    <row r="74" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX73" s="5"/>
+      <c r="AY73" s="5"/>
+    </row>
+    <row r="74" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
@@ -6190,8 +6448,10 @@
       <c r="AU74" s="5"/>
       <c r="AV74" s="5"/>
       <c r="AW74" s="5"/>
-    </row>
-    <row r="75" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX74" s="5"/>
+      <c r="AY74" s="5"/>
+    </row>
+    <row r="75" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
@@ -6239,8 +6499,10 @@
       <c r="AU75" s="5"/>
       <c r="AV75" s="5"/>
       <c r="AW75" s="5"/>
-    </row>
-    <row r="76" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX75" s="5"/>
+      <c r="AY75" s="5"/>
+    </row>
+    <row r="76" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
@@ -6288,8 +6550,10 @@
       <c r="AU76" s="5"/>
       <c r="AV76" s="5"/>
       <c r="AW76" s="5"/>
-    </row>
-    <row r="77" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX76" s="5"/>
+      <c r="AY76" s="5"/>
+    </row>
+    <row r="77" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
@@ -6337,8 +6601,10 @@
       <c r="AU77" s="5"/>
       <c r="AV77" s="5"/>
       <c r="AW77" s="5"/>
-    </row>
-    <row r="78" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX77" s="5"/>
+      <c r="AY77" s="5"/>
+    </row>
+    <row r="78" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
@@ -6386,8 +6652,10 @@
       <c r="AU78" s="5"/>
       <c r="AV78" s="5"/>
       <c r="AW78" s="5"/>
-    </row>
-    <row r="79" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX78" s="5"/>
+      <c r="AY78" s="5"/>
+    </row>
+    <row r="79" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
@@ -6435,8 +6703,10 @@
       <c r="AU79" s="5"/>
       <c r="AV79" s="5"/>
       <c r="AW79" s="5"/>
-    </row>
-    <row r="80" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX79" s="5"/>
+      <c r="AY79" s="5"/>
+    </row>
+    <row r="80" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
@@ -6484,8 +6754,10 @@
       <c r="AU80" s="5"/>
       <c r="AV80" s="5"/>
       <c r="AW80" s="5"/>
-    </row>
-    <row r="81" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX80" s="5"/>
+      <c r="AY80" s="5"/>
+    </row>
+    <row r="81" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
@@ -6533,8 +6805,10 @@
       <c r="AU81" s="5"/>
       <c r="AV81" s="5"/>
       <c r="AW81" s="5"/>
-    </row>
-    <row r="82" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX81" s="5"/>
+      <c r="AY81" s="5"/>
+    </row>
+    <row r="82" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
       <c r="E82" s="5"/>
@@ -6582,8 +6856,10 @@
       <c r="AU82" s="5"/>
       <c r="AV82" s="5"/>
       <c r="AW82" s="5"/>
-    </row>
-    <row r="83" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX82" s="5"/>
+      <c r="AY82" s="5"/>
+    </row>
+    <row r="83" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
@@ -6631,8 +6907,10 @@
       <c r="AU83" s="5"/>
       <c r="AV83" s="5"/>
       <c r="AW83" s="5"/>
-    </row>
-    <row r="84" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX83" s="5"/>
+      <c r="AY83" s="5"/>
+    </row>
+    <row r="84" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C84" s="5"/>
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
@@ -6680,8 +6958,10 @@
       <c r="AU84" s="5"/>
       <c r="AV84" s="5"/>
       <c r="AW84" s="5"/>
-    </row>
-    <row r="85" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX84" s="5"/>
+      <c r="AY84" s="5"/>
+    </row>
+    <row r="85" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C85" s="5"/>
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
@@ -6729,8 +7009,10 @@
       <c r="AU85" s="5"/>
       <c r="AV85" s="5"/>
       <c r="AW85" s="5"/>
-    </row>
-    <row r="86" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX85" s="5"/>
+      <c r="AY85" s="5"/>
+    </row>
+    <row r="86" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C86" s="5"/>
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
@@ -6778,8 +7060,10 @@
       <c r="AU86" s="5"/>
       <c r="AV86" s="5"/>
       <c r="AW86" s="5"/>
-    </row>
-    <row r="87" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX86" s="5"/>
+      <c r="AY86" s="5"/>
+    </row>
+    <row r="87" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
@@ -6827,8 +7111,10 @@
       <c r="AU87" s="5"/>
       <c r="AV87" s="5"/>
       <c r="AW87" s="5"/>
-    </row>
-    <row r="88" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX87" s="5"/>
+      <c r="AY87" s="5"/>
+    </row>
+    <row r="88" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C88" s="5"/>
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
@@ -6876,8 +7162,10 @@
       <c r="AU88" s="5"/>
       <c r="AV88" s="5"/>
       <c r="AW88" s="5"/>
-    </row>
-    <row r="89" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX88" s="5"/>
+      <c r="AY88" s="5"/>
+    </row>
+    <row r="89" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C89" s="5"/>
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
@@ -6925,8 +7213,10 @@
       <c r="AU89" s="5"/>
       <c r="AV89" s="5"/>
       <c r="AW89" s="5"/>
-    </row>
-    <row r="90" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX89" s="5"/>
+      <c r="AY89" s="5"/>
+    </row>
+    <row r="90" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C90" s="5"/>
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
@@ -6974,8 +7264,10 @@
       <c r="AU90" s="5"/>
       <c r="AV90" s="5"/>
       <c r="AW90" s="5"/>
-    </row>
-    <row r="91" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX90" s="5"/>
+      <c r="AY90" s="5"/>
+    </row>
+    <row r="91" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
@@ -7023,8 +7315,10 @@
       <c r="AU91" s="5"/>
       <c r="AV91" s="5"/>
       <c r="AW91" s="5"/>
-    </row>
-    <row r="92" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX91" s="5"/>
+      <c r="AY91" s="5"/>
+    </row>
+    <row r="92" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
@@ -7072,8 +7366,10 @@
       <c r="AU92" s="5"/>
       <c r="AV92" s="5"/>
       <c r="AW92" s="5"/>
-    </row>
-    <row r="93" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX92" s="5"/>
+      <c r="AY92" s="5"/>
+    </row>
+    <row r="93" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
@@ -7121,8 +7417,10 @@
       <c r="AU93" s="5"/>
       <c r="AV93" s="5"/>
       <c r="AW93" s="5"/>
-    </row>
-    <row r="94" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX93" s="5"/>
+      <c r="AY93" s="5"/>
+    </row>
+    <row r="94" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C94" s="5"/>
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
@@ -7170,8 +7468,10 @@
       <c r="AU94" s="5"/>
       <c r="AV94" s="5"/>
       <c r="AW94" s="5"/>
-    </row>
-    <row r="95" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX94" s="5"/>
+      <c r="AY94" s="5"/>
+    </row>
+    <row r="95" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
@@ -7219,8 +7519,10 @@
       <c r="AU95" s="5"/>
       <c r="AV95" s="5"/>
       <c r="AW95" s="5"/>
-    </row>
-    <row r="96" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX95" s="5"/>
+      <c r="AY95" s="5"/>
+    </row>
+    <row r="96" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C96" s="5"/>
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
@@ -7268,8 +7570,10 @@
       <c r="AU96" s="5"/>
       <c r="AV96" s="5"/>
       <c r="AW96" s="5"/>
-    </row>
-    <row r="97" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX96" s="5"/>
+      <c r="AY96" s="5"/>
+    </row>
+    <row r="97" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C97" s="5"/>
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
@@ -7317,8 +7621,10 @@
       <c r="AU97" s="5"/>
       <c r="AV97" s="5"/>
       <c r="AW97" s="5"/>
-    </row>
-    <row r="98" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX97" s="5"/>
+      <c r="AY97" s="5"/>
+    </row>
+    <row r="98" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C98" s="5"/>
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
@@ -7366,8 +7672,10 @@
       <c r="AU98" s="5"/>
       <c r="AV98" s="5"/>
       <c r="AW98" s="5"/>
-    </row>
-    <row r="99" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX98" s="5"/>
+      <c r="AY98" s="5"/>
+    </row>
+    <row r="99" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
@@ -7415,8 +7723,10 @@
       <c r="AU99" s="5"/>
       <c r="AV99" s="5"/>
       <c r="AW99" s="5"/>
-    </row>
-    <row r="100" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX99" s="5"/>
+      <c r="AY99" s="5"/>
+    </row>
+    <row r="100" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C100" s="5"/>
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
@@ -7464,8 +7774,10 @@
       <c r="AU100" s="5"/>
       <c r="AV100" s="5"/>
       <c r="AW100" s="5"/>
-    </row>
-    <row r="101" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX100" s="5"/>
+      <c r="AY100" s="5"/>
+    </row>
+    <row r="101" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C101" s="5"/>
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
@@ -7513,8 +7825,10 @@
       <c r="AU101" s="5"/>
       <c r="AV101" s="5"/>
       <c r="AW101" s="5"/>
-    </row>
-    <row r="102" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX101" s="5"/>
+      <c r="AY101" s="5"/>
+    </row>
+    <row r="102" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C102" s="5"/>
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
@@ -7562,8 +7876,10 @@
       <c r="AU102" s="5"/>
       <c r="AV102" s="5"/>
       <c r="AW102" s="5"/>
-    </row>
-    <row r="103" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX102" s="5"/>
+      <c r="AY102" s="5"/>
+    </row>
+    <row r="103" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C103" s="5"/>
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
@@ -7611,8 +7927,10 @@
       <c r="AU103" s="5"/>
       <c r="AV103" s="5"/>
       <c r="AW103" s="5"/>
-    </row>
-    <row r="104" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX103" s="5"/>
+      <c r="AY103" s="5"/>
+    </row>
+    <row r="104" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C104" s="5"/>
       <c r="D104" s="5"/>
       <c r="E104" s="5"/>
@@ -7660,8 +7978,10 @@
       <c r="AU104" s="5"/>
       <c r="AV104" s="5"/>
       <c r="AW104" s="5"/>
-    </row>
-    <row r="105" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX104" s="5"/>
+      <c r="AY104" s="5"/>
+    </row>
+    <row r="105" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C105" s="5"/>
       <c r="D105" s="5"/>
       <c r="E105" s="5"/>
@@ -7709,8 +8029,10 @@
       <c r="AU105" s="5"/>
       <c r="AV105" s="5"/>
       <c r="AW105" s="5"/>
-    </row>
-    <row r="106" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX105" s="5"/>
+      <c r="AY105" s="5"/>
+    </row>
+    <row r="106" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C106" s="5"/>
       <c r="D106" s="5"/>
       <c r="E106" s="5"/>
@@ -7758,8 +8080,10 @@
       <c r="AU106" s="5"/>
       <c r="AV106" s="5"/>
       <c r="AW106" s="5"/>
-    </row>
-    <row r="107" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX106" s="5"/>
+      <c r="AY106" s="5"/>
+    </row>
+    <row r="107" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C107" s="5"/>
       <c r="D107" s="5"/>
       <c r="E107" s="5"/>
@@ -7807,8 +8131,10 @@
       <c r="AU107" s="5"/>
       <c r="AV107" s="5"/>
       <c r="AW107" s="5"/>
-    </row>
-    <row r="108" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX107" s="5"/>
+      <c r="AY107" s="5"/>
+    </row>
+    <row r="108" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C108" s="5"/>
       <c r="D108" s="5"/>
       <c r="E108" s="5"/>
@@ -7856,8 +8182,10 @@
       <c r="AU108" s="5"/>
       <c r="AV108" s="5"/>
       <c r="AW108" s="5"/>
-    </row>
-    <row r="109" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX108" s="5"/>
+      <c r="AY108" s="5"/>
+    </row>
+    <row r="109" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C109" s="5"/>
       <c r="D109" s="5"/>
       <c r="E109" s="5"/>
@@ -7905,8 +8233,10 @@
       <c r="AU109" s="5"/>
       <c r="AV109" s="5"/>
       <c r="AW109" s="5"/>
-    </row>
-    <row r="110" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX109" s="5"/>
+      <c r="AY109" s="5"/>
+    </row>
+    <row r="110" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C110" s="5"/>
       <c r="D110" s="5"/>
       <c r="E110" s="5"/>
@@ -7954,8 +8284,10 @@
       <c r="AU110" s="5"/>
       <c r="AV110" s="5"/>
       <c r="AW110" s="5"/>
-    </row>
-    <row r="111" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX110" s="5"/>
+      <c r="AY110" s="5"/>
+    </row>
+    <row r="111" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C111" s="5"/>
       <c r="D111" s="5"/>
       <c r="E111" s="5"/>
@@ -8003,8 +8335,10 @@
       <c r="AU111" s="5"/>
       <c r="AV111" s="5"/>
       <c r="AW111" s="5"/>
-    </row>
-    <row r="112" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX111" s="5"/>
+      <c r="AY111" s="5"/>
+    </row>
+    <row r="112" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C112" s="5"/>
       <c r="D112" s="5"/>
       <c r="E112" s="5"/>
@@ -8052,8 +8386,10 @@
       <c r="AU112" s="5"/>
       <c r="AV112" s="5"/>
       <c r="AW112" s="5"/>
-    </row>
-    <row r="113" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX112" s="5"/>
+      <c r="AY112" s="5"/>
+    </row>
+    <row r="113" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C113" s="5"/>
       <c r="D113" s="5"/>
       <c r="E113" s="5"/>
@@ -8101,8 +8437,10 @@
       <c r="AU113" s="5"/>
       <c r="AV113" s="5"/>
       <c r="AW113" s="5"/>
-    </row>
-    <row r="114" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX113" s="5"/>
+      <c r="AY113" s="5"/>
+    </row>
+    <row r="114" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C114" s="5"/>
       <c r="D114" s="5"/>
       <c r="E114" s="5"/>
@@ -8150,8 +8488,10 @@
       <c r="AU114" s="5"/>
       <c r="AV114" s="5"/>
       <c r="AW114" s="5"/>
-    </row>
-    <row r="115" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX114" s="5"/>
+      <c r="AY114" s="5"/>
+    </row>
+    <row r="115" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C115" s="5"/>
       <c r="D115" s="5"/>
       <c r="E115" s="5"/>
@@ -8199,8 +8539,10 @@
       <c r="AU115" s="5"/>
       <c r="AV115" s="5"/>
       <c r="AW115" s="5"/>
-    </row>
-    <row r="116" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX115" s="5"/>
+      <c r="AY115" s="5"/>
+    </row>
+    <row r="116" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C116" s="5"/>
       <c r="D116" s="5"/>
       <c r="E116" s="5"/>
@@ -8248,8 +8590,10 @@
       <c r="AU116" s="5"/>
       <c r="AV116" s="5"/>
       <c r="AW116" s="5"/>
-    </row>
-    <row r="117" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX116" s="5"/>
+      <c r="AY116" s="5"/>
+    </row>
+    <row r="117" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C117" s="5"/>
       <c r="D117" s="5"/>
       <c r="E117" s="5"/>
@@ -8297,8 +8641,10 @@
       <c r="AU117" s="5"/>
       <c r="AV117" s="5"/>
       <c r="AW117" s="5"/>
-    </row>
-    <row r="118" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX117" s="5"/>
+      <c r="AY117" s="5"/>
+    </row>
+    <row r="118" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C118" s="5"/>
       <c r="D118" s="5"/>
       <c r="E118" s="5"/>
@@ -8346,8 +8692,10 @@
       <c r="AU118" s="5"/>
       <c r="AV118" s="5"/>
       <c r="AW118" s="5"/>
-    </row>
-    <row r="119" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX118" s="5"/>
+      <c r="AY118" s="5"/>
+    </row>
+    <row r="119" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C119" s="5"/>
       <c r="D119" s="5"/>
       <c r="E119" s="5"/>
@@ -8395,8 +8743,10 @@
       <c r="AU119" s="5"/>
       <c r="AV119" s="5"/>
       <c r="AW119" s="5"/>
-    </row>
-    <row r="120" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX119" s="5"/>
+      <c r="AY119" s="5"/>
+    </row>
+    <row r="120" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C120" s="5"/>
       <c r="D120" s="5"/>
       <c r="E120" s="5"/>
@@ -8444,8 +8794,10 @@
       <c r="AU120" s="5"/>
       <c r="AV120" s="5"/>
       <c r="AW120" s="5"/>
-    </row>
-    <row r="121" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX120" s="5"/>
+      <c r="AY120" s="5"/>
+    </row>
+    <row r="121" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C121" s="5"/>
       <c r="D121" s="5"/>
       <c r="E121" s="5"/>
@@ -8493,8 +8845,10 @@
       <c r="AU121" s="5"/>
       <c r="AV121" s="5"/>
       <c r="AW121" s="5"/>
-    </row>
-    <row r="122" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX121" s="5"/>
+      <c r="AY121" s="5"/>
+    </row>
+    <row r="122" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C122" s="5"/>
       <c r="D122" s="5"/>
       <c r="E122" s="5"/>
@@ -8542,8 +8896,10 @@
       <c r="AU122" s="5"/>
       <c r="AV122" s="5"/>
       <c r="AW122" s="5"/>
-    </row>
-    <row r="123" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX122" s="5"/>
+      <c r="AY122" s="5"/>
+    </row>
+    <row r="123" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C123" s="5"/>
       <c r="D123" s="5"/>
       <c r="E123" s="5"/>
@@ -8591,8 +8947,10 @@
       <c r="AU123" s="5"/>
       <c r="AV123" s="5"/>
       <c r="AW123" s="5"/>
-    </row>
-    <row r="124" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX123" s="5"/>
+      <c r="AY123" s="5"/>
+    </row>
+    <row r="124" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C124" s="5"/>
       <c r="D124" s="5"/>
       <c r="E124" s="5"/>
@@ -8640,8 +8998,10 @@
       <c r="AU124" s="5"/>
       <c r="AV124" s="5"/>
       <c r="AW124" s="5"/>
-    </row>
-    <row r="125" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX124" s="5"/>
+      <c r="AY124" s="5"/>
+    </row>
+    <row r="125" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C125" s="5"/>
       <c r="D125" s="5"/>
       <c r="E125" s="5"/>
@@ -8689,8 +9049,10 @@
       <c r="AU125" s="5"/>
       <c r="AV125" s="5"/>
       <c r="AW125" s="5"/>
-    </row>
-    <row r="126" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX125" s="5"/>
+      <c r="AY125" s="5"/>
+    </row>
+    <row r="126" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C126" s="5"/>
       <c r="D126" s="5"/>
       <c r="E126" s="5"/>
@@ -8738,8 +9100,10 @@
       <c r="AU126" s="5"/>
       <c r="AV126" s="5"/>
       <c r="AW126" s="5"/>
-    </row>
-    <row r="127" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX126" s="5"/>
+      <c r="AY126" s="5"/>
+    </row>
+    <row r="127" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C127" s="5"/>
       <c r="D127" s="5"/>
       <c r="E127" s="5"/>
@@ -8787,8 +9151,10 @@
       <c r="AU127" s="5"/>
       <c r="AV127" s="5"/>
       <c r="AW127" s="5"/>
-    </row>
-    <row r="128" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX127" s="5"/>
+      <c r="AY127" s="5"/>
+    </row>
+    <row r="128" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C128" s="5"/>
       <c r="D128" s="5"/>
       <c r="E128" s="5"/>
@@ -8836,8 +9202,10 @@
       <c r="AU128" s="5"/>
       <c r="AV128" s="5"/>
       <c r="AW128" s="5"/>
-    </row>
-    <row r="129" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX128" s="5"/>
+      <c r="AY128" s="5"/>
+    </row>
+    <row r="129" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C129" s="5"/>
       <c r="D129" s="5"/>
       <c r="E129" s="5"/>
@@ -8885,8 +9253,10 @@
       <c r="AU129" s="5"/>
       <c r="AV129" s="5"/>
       <c r="AW129" s="5"/>
-    </row>
-    <row r="130" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX129" s="5"/>
+      <c r="AY129" s="5"/>
+    </row>
+    <row r="130" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C130" s="5"/>
       <c r="D130" s="5"/>
       <c r="E130" s="5"/>
@@ -8934,8 +9304,10 @@
       <c r="AU130" s="5"/>
       <c r="AV130" s="5"/>
       <c r="AW130" s="5"/>
-    </row>
-    <row r="131" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX130" s="5"/>
+      <c r="AY130" s="5"/>
+    </row>
+    <row r="131" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C131" s="5"/>
       <c r="D131" s="5"/>
       <c r="E131" s="5"/>
@@ -8983,8 +9355,10 @@
       <c r="AU131" s="5"/>
       <c r="AV131" s="5"/>
       <c r="AW131" s="5"/>
-    </row>
-    <row r="132" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX131" s="5"/>
+      <c r="AY131" s="5"/>
+    </row>
+    <row r="132" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C132" s="5"/>
       <c r="D132" s="5"/>
       <c r="E132" s="5"/>
@@ -9032,8 +9406,10 @@
       <c r="AU132" s="5"/>
       <c r="AV132" s="5"/>
       <c r="AW132" s="5"/>
-    </row>
-    <row r="133" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX132" s="5"/>
+      <c r="AY132" s="5"/>
+    </row>
+    <row r="133" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C133" s="5"/>
       <c r="D133" s="5"/>
       <c r="E133" s="5"/>
@@ -9081,8 +9457,10 @@
       <c r="AU133" s="5"/>
       <c r="AV133" s="5"/>
       <c r="AW133" s="5"/>
-    </row>
-    <row r="134" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX133" s="5"/>
+      <c r="AY133" s="5"/>
+    </row>
+    <row r="134" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C134" s="5"/>
       <c r="D134" s="5"/>
       <c r="E134" s="5"/>
@@ -9130,8 +9508,10 @@
       <c r="AU134" s="5"/>
       <c r="AV134" s="5"/>
       <c r="AW134" s="5"/>
-    </row>
-    <row r="135" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX134" s="5"/>
+      <c r="AY134" s="5"/>
+    </row>
+    <row r="135" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C135" s="5"/>
       <c r="D135" s="5"/>
       <c r="E135" s="5"/>
@@ -9179,8 +9559,10 @@
       <c r="AU135" s="5"/>
       <c r="AV135" s="5"/>
       <c r="AW135" s="5"/>
-    </row>
-    <row r="136" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX135" s="5"/>
+      <c r="AY135" s="5"/>
+    </row>
+    <row r="136" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C136" s="5"/>
       <c r="D136" s="5"/>
       <c r="E136" s="5"/>
@@ -9228,8 +9610,10 @@
       <c r="AU136" s="5"/>
       <c r="AV136" s="5"/>
       <c r="AW136" s="5"/>
-    </row>
-    <row r="137" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX136" s="5"/>
+      <c r="AY136" s="5"/>
+    </row>
+    <row r="137" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C137" s="5"/>
       <c r="D137" s="5"/>
       <c r="E137" s="5"/>
@@ -9277,8 +9661,10 @@
       <c r="AU137" s="5"/>
       <c r="AV137" s="5"/>
       <c r="AW137" s="5"/>
-    </row>
-    <row r="138" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX137" s="5"/>
+      <c r="AY137" s="5"/>
+    </row>
+    <row r="138" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C138" s="5"/>
       <c r="D138" s="5"/>
       <c r="E138" s="5"/>
@@ -9326,8 +9712,10 @@
       <c r="AU138" s="5"/>
       <c r="AV138" s="5"/>
       <c r="AW138" s="5"/>
-    </row>
-    <row r="139" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX138" s="5"/>
+      <c r="AY138" s="5"/>
+    </row>
+    <row r="139" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C139" s="5"/>
       <c r="D139" s="5"/>
       <c r="E139" s="5"/>
@@ -9375,8 +9763,10 @@
       <c r="AU139" s="5"/>
       <c r="AV139" s="5"/>
       <c r="AW139" s="5"/>
-    </row>
-    <row r="140" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX139" s="5"/>
+      <c r="AY139" s="5"/>
+    </row>
+    <row r="140" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C140" s="5"/>
       <c r="D140" s="5"/>
       <c r="E140" s="5"/>
@@ -9424,8 +9814,10 @@
       <c r="AU140" s="5"/>
       <c r="AV140" s="5"/>
       <c r="AW140" s="5"/>
-    </row>
-    <row r="141" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX140" s="5"/>
+      <c r="AY140" s="5"/>
+    </row>
+    <row r="141" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C141" s="5"/>
       <c r="D141" s="5"/>
       <c r="E141" s="5"/>
@@ -9473,8 +9865,10 @@
       <c r="AU141" s="5"/>
       <c r="AV141" s="5"/>
       <c r="AW141" s="5"/>
-    </row>
-    <row r="142" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX141" s="5"/>
+      <c r="AY141" s="5"/>
+    </row>
+    <row r="142" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C142" s="5"/>
       <c r="D142" s="5"/>
       <c r="E142" s="5"/>
@@ -9522,8 +9916,10 @@
       <c r="AU142" s="5"/>
       <c r="AV142" s="5"/>
       <c r="AW142" s="5"/>
-    </row>
-    <row r="143" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX142" s="5"/>
+      <c r="AY142" s="5"/>
+    </row>
+    <row r="143" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C143" s="5"/>
       <c r="D143" s="5"/>
       <c r="E143" s="5"/>
@@ -9571,8 +9967,10 @@
       <c r="AU143" s="5"/>
       <c r="AV143" s="5"/>
       <c r="AW143" s="5"/>
-    </row>
-    <row r="144" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX143" s="5"/>
+      <c r="AY143" s="5"/>
+    </row>
+    <row r="144" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C144" s="5"/>
       <c r="D144" s="5"/>
       <c r="E144" s="5"/>
@@ -9620,8 +10018,10 @@
       <c r="AU144" s="5"/>
       <c r="AV144" s="5"/>
       <c r="AW144" s="5"/>
-    </row>
-    <row r="145" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX144" s="5"/>
+      <c r="AY144" s="5"/>
+    </row>
+    <row r="145" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C145" s="5"/>
       <c r="D145" s="5"/>
       <c r="E145" s="5"/>
@@ -9669,8 +10069,10 @@
       <c r="AU145" s="5"/>
       <c r="AV145" s="5"/>
       <c r="AW145" s="5"/>
-    </row>
-    <row r="146" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX145" s="5"/>
+      <c r="AY145" s="5"/>
+    </row>
+    <row r="146" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C146" s="5"/>
       <c r="D146" s="5"/>
       <c r="E146" s="5"/>
@@ -9718,8 +10120,10 @@
       <c r="AU146" s="5"/>
       <c r="AV146" s="5"/>
       <c r="AW146" s="5"/>
-    </row>
-    <row r="147" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX146" s="5"/>
+      <c r="AY146" s="5"/>
+    </row>
+    <row r="147" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C147" s="5"/>
       <c r="D147" s="5"/>
       <c r="E147" s="5"/>
@@ -9767,8 +10171,10 @@
       <c r="AU147" s="5"/>
       <c r="AV147" s="5"/>
       <c r="AW147" s="5"/>
-    </row>
-    <row r="148" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX147" s="5"/>
+      <c r="AY147" s="5"/>
+    </row>
+    <row r="148" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C148" s="5"/>
       <c r="D148" s="5"/>
       <c r="E148" s="5"/>
@@ -9816,8 +10222,10 @@
       <c r="AU148" s="5"/>
       <c r="AV148" s="5"/>
       <c r="AW148" s="5"/>
-    </row>
-    <row r="149" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX148" s="5"/>
+      <c r="AY148" s="5"/>
+    </row>
+    <row r="149" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C149" s="5"/>
       <c r="D149" s="5"/>
       <c r="E149" s="5"/>
@@ -9865,8 +10273,10 @@
       <c r="AU149" s="5"/>
       <c r="AV149" s="5"/>
       <c r="AW149" s="5"/>
-    </row>
-    <row r="150" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX149" s="5"/>
+      <c r="AY149" s="5"/>
+    </row>
+    <row r="150" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C150" s="5"/>
       <c r="D150" s="5"/>
       <c r="E150" s="5"/>
@@ -9914,8 +10324,10 @@
       <c r="AU150" s="5"/>
       <c r="AV150" s="5"/>
       <c r="AW150" s="5"/>
-    </row>
-    <row r="151" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX150" s="5"/>
+      <c r="AY150" s="5"/>
+    </row>
+    <row r="151" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C151" s="5"/>
       <c r="D151" s="5"/>
       <c r="E151" s="5"/>
@@ -9963,8 +10375,10 @@
       <c r="AU151" s="5"/>
       <c r="AV151" s="5"/>
       <c r="AW151" s="5"/>
-    </row>
-    <row r="152" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX151" s="5"/>
+      <c r="AY151" s="5"/>
+    </row>
+    <row r="152" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C152" s="5"/>
       <c r="D152" s="5"/>
       <c r="E152" s="5"/>
@@ -10012,8 +10426,10 @@
       <c r="AU152" s="5"/>
       <c r="AV152" s="5"/>
       <c r="AW152" s="5"/>
-    </row>
-    <row r="153" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX152" s="5"/>
+      <c r="AY152" s="5"/>
+    </row>
+    <row r="153" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C153" s="5"/>
       <c r="D153" s="5"/>
       <c r="E153" s="5"/>
@@ -10061,8 +10477,10 @@
       <c r="AU153" s="5"/>
       <c r="AV153" s="5"/>
       <c r="AW153" s="5"/>
-    </row>
-    <row r="154" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX153" s="5"/>
+      <c r="AY153" s="5"/>
+    </row>
+    <row r="154" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C154" s="5"/>
       <c r="D154" s="5"/>
       <c r="E154" s="5"/>
@@ -10110,8 +10528,10 @@
       <c r="AU154" s="5"/>
       <c r="AV154" s="5"/>
       <c r="AW154" s="5"/>
-    </row>
-    <row r="155" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX154" s="5"/>
+      <c r="AY154" s="5"/>
+    </row>
+    <row r="155" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C155" s="5"/>
       <c r="D155" s="5"/>
       <c r="E155" s="5"/>
@@ -10159,8 +10579,10 @@
       <c r="AU155" s="5"/>
       <c r="AV155" s="5"/>
       <c r="AW155" s="5"/>
-    </row>
-    <row r="156" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX155" s="5"/>
+      <c r="AY155" s="5"/>
+    </row>
+    <row r="156" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C156" s="5"/>
       <c r="D156" s="5"/>
       <c r="E156" s="5"/>
@@ -10208,8 +10630,10 @@
       <c r="AU156" s="5"/>
       <c r="AV156" s="5"/>
       <c r="AW156" s="5"/>
-    </row>
-    <row r="157" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX156" s="5"/>
+      <c r="AY156" s="5"/>
+    </row>
+    <row r="157" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C157" s="5"/>
       <c r="D157" s="5"/>
       <c r="E157" s="5"/>
@@ -10257,8 +10681,10 @@
       <c r="AU157" s="5"/>
       <c r="AV157" s="5"/>
       <c r="AW157" s="5"/>
-    </row>
-    <row r="158" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX157" s="5"/>
+      <c r="AY157" s="5"/>
+    </row>
+    <row r="158" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C158" s="5"/>
       <c r="D158" s="5"/>
       <c r="E158" s="5"/>
@@ -10306,8 +10732,10 @@
       <c r="AU158" s="5"/>
       <c r="AV158" s="5"/>
       <c r="AW158" s="5"/>
-    </row>
-    <row r="159" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX158" s="5"/>
+      <c r="AY158" s="5"/>
+    </row>
+    <row r="159" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C159" s="5"/>
       <c r="D159" s="5"/>
       <c r="E159" s="5"/>
@@ -10355,8 +10783,10 @@
       <c r="AU159" s="5"/>
       <c r="AV159" s="5"/>
       <c r="AW159" s="5"/>
-    </row>
-    <row r="160" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX159" s="5"/>
+      <c r="AY159" s="5"/>
+    </row>
+    <row r="160" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C160" s="5"/>
       <c r="D160" s="5"/>
       <c r="E160" s="5"/>
@@ -10404,8 +10834,10 @@
       <c r="AU160" s="5"/>
       <c r="AV160" s="5"/>
       <c r="AW160" s="5"/>
-    </row>
-    <row r="161" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX160" s="5"/>
+      <c r="AY160" s="5"/>
+    </row>
+    <row r="161" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C161" s="5"/>
       <c r="D161" s="5"/>
       <c r="E161" s="5"/>
@@ -10453,8 +10885,10 @@
       <c r="AU161" s="5"/>
       <c r="AV161" s="5"/>
       <c r="AW161" s="5"/>
-    </row>
-    <row r="162" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX161" s="5"/>
+      <c r="AY161" s="5"/>
+    </row>
+    <row r="162" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C162" s="5"/>
       <c r="D162" s="5"/>
       <c r="E162" s="5"/>
@@ -10502,8 +10936,10 @@
       <c r="AU162" s="5"/>
       <c r="AV162" s="5"/>
       <c r="AW162" s="5"/>
-    </row>
-    <row r="163" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX162" s="5"/>
+      <c r="AY162" s="5"/>
+    </row>
+    <row r="163" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C163" s="5"/>
       <c r="D163" s="5"/>
       <c r="E163" s="5"/>
@@ -10551,8 +10987,10 @@
       <c r="AU163" s="5"/>
       <c r="AV163" s="5"/>
       <c r="AW163" s="5"/>
-    </row>
-    <row r="164" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX163" s="5"/>
+      <c r="AY163" s="5"/>
+    </row>
+    <row r="164" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C164" s="5"/>
       <c r="D164" s="5"/>
       <c r="E164" s="5"/>
@@ -10600,8 +11038,10 @@
       <c r="AU164" s="5"/>
       <c r="AV164" s="5"/>
       <c r="AW164" s="5"/>
-    </row>
-    <row r="165" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX164" s="5"/>
+      <c r="AY164" s="5"/>
+    </row>
+    <row r="165" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C165" s="5"/>
       <c r="D165" s="5"/>
       <c r="E165" s="5"/>
@@ -10649,8 +11089,10 @@
       <c r="AU165" s="5"/>
       <c r="AV165" s="5"/>
       <c r="AW165" s="5"/>
-    </row>
-    <row r="166" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX165" s="5"/>
+      <c r="AY165" s="5"/>
+    </row>
+    <row r="166" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C166" s="5"/>
       <c r="D166" s="5"/>
       <c r="E166" s="5"/>
@@ -10698,8 +11140,10 @@
       <c r="AU166" s="5"/>
       <c r="AV166" s="5"/>
       <c r="AW166" s="5"/>
-    </row>
-    <row r="167" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX166" s="5"/>
+      <c r="AY166" s="5"/>
+    </row>
+    <row r="167" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C167" s="5"/>
       <c r="D167" s="5"/>
       <c r="E167" s="5"/>
@@ -10747,8 +11191,10 @@
       <c r="AU167" s="5"/>
       <c r="AV167" s="5"/>
       <c r="AW167" s="5"/>
-    </row>
-    <row r="168" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX167" s="5"/>
+      <c r="AY167" s="5"/>
+    </row>
+    <row r="168" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C168" s="5"/>
       <c r="D168" s="5"/>
       <c r="E168" s="5"/>
@@ -10796,8 +11242,10 @@
       <c r="AU168" s="5"/>
       <c r="AV168" s="5"/>
       <c r="AW168" s="5"/>
-    </row>
-    <row r="169" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX168" s="5"/>
+      <c r="AY168" s="5"/>
+    </row>
+    <row r="169" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C169" s="5"/>
       <c r="D169" s="5"/>
       <c r="E169" s="5"/>
@@ -10845,8 +11293,10 @@
       <c r="AU169" s="5"/>
       <c r="AV169" s="5"/>
       <c r="AW169" s="5"/>
-    </row>
-    <row r="170" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX169" s="5"/>
+      <c r="AY169" s="5"/>
+    </row>
+    <row r="170" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C170" s="5"/>
       <c r="D170" s="5"/>
       <c r="E170" s="5"/>
@@ -10894,8 +11344,10 @@
       <c r="AU170" s="5"/>
       <c r="AV170" s="5"/>
       <c r="AW170" s="5"/>
-    </row>
-    <row r="171" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX170" s="5"/>
+      <c r="AY170" s="5"/>
+    </row>
+    <row r="171" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C171" s="5"/>
       <c r="D171" s="5"/>
       <c r="E171" s="5"/>
@@ -10943,8 +11395,10 @@
       <c r="AU171" s="5"/>
       <c r="AV171" s="5"/>
       <c r="AW171" s="5"/>
-    </row>
-    <row r="172" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX171" s="5"/>
+      <c r="AY171" s="5"/>
+    </row>
+    <row r="172" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C172" s="5"/>
       <c r="D172" s="5"/>
       <c r="E172" s="5"/>
@@ -10992,8 +11446,10 @@
       <c r="AU172" s="5"/>
       <c r="AV172" s="5"/>
       <c r="AW172" s="5"/>
-    </row>
-    <row r="173" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX172" s="5"/>
+      <c r="AY172" s="5"/>
+    </row>
+    <row r="173" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C173" s="5"/>
       <c r="D173" s="5"/>
       <c r="E173" s="5"/>
@@ -11041,8 +11497,10 @@
       <c r="AU173" s="5"/>
       <c r="AV173" s="5"/>
       <c r="AW173" s="5"/>
-    </row>
-    <row r="174" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX173" s="5"/>
+      <c r="AY173" s="5"/>
+    </row>
+    <row r="174" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C174" s="5"/>
       <c r="D174" s="5"/>
       <c r="E174" s="5"/>
@@ -11090,8 +11548,10 @@
       <c r="AU174" s="5"/>
       <c r="AV174" s="5"/>
       <c r="AW174" s="5"/>
-    </row>
-    <row r="175" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX174" s="5"/>
+      <c r="AY174" s="5"/>
+    </row>
+    <row r="175" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C175" s="5"/>
       <c r="D175" s="5"/>
       <c r="E175" s="5"/>
@@ -11139,8 +11599,10 @@
       <c r="AU175" s="5"/>
       <c r="AV175" s="5"/>
       <c r="AW175" s="5"/>
-    </row>
-    <row r="176" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX175" s="5"/>
+      <c r="AY175" s="5"/>
+    </row>
+    <row r="176" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C176" s="5"/>
       <c r="D176" s="5"/>
       <c r="E176" s="5"/>
@@ -11188,8 +11650,10 @@
       <c r="AU176" s="5"/>
       <c r="AV176" s="5"/>
       <c r="AW176" s="5"/>
-    </row>
-    <row r="177" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX176" s="5"/>
+      <c r="AY176" s="5"/>
+    </row>
+    <row r="177" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C177" s="5"/>
       <c r="D177" s="5"/>
       <c r="E177" s="5"/>
@@ -11237,8 +11701,10 @@
       <c r="AU177" s="5"/>
       <c r="AV177" s="5"/>
       <c r="AW177" s="5"/>
-    </row>
-    <row r="178" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX177" s="5"/>
+      <c r="AY177" s="5"/>
+    </row>
+    <row r="178" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C178" s="5"/>
       <c r="D178" s="5"/>
       <c r="E178" s="5"/>
@@ -11286,8 +11752,10 @@
       <c r="AU178" s="5"/>
       <c r="AV178" s="5"/>
       <c r="AW178" s="5"/>
-    </row>
-    <row r="179" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX178" s="5"/>
+      <c r="AY178" s="5"/>
+    </row>
+    <row r="179" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C179" s="5"/>
       <c r="D179" s="5"/>
       <c r="E179" s="5"/>
@@ -11335,8 +11803,10 @@
       <c r="AU179" s="5"/>
       <c r="AV179" s="5"/>
       <c r="AW179" s="5"/>
-    </row>
-    <row r="180" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX179" s="5"/>
+      <c r="AY179" s="5"/>
+    </row>
+    <row r="180" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C180" s="5"/>
       <c r="D180" s="5"/>
       <c r="E180" s="5"/>
@@ -11384,8 +11854,10 @@
       <c r="AU180" s="5"/>
       <c r="AV180" s="5"/>
       <c r="AW180" s="5"/>
-    </row>
-    <row r="181" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX180" s="5"/>
+      <c r="AY180" s="5"/>
+    </row>
+    <row r="181" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C181" s="5"/>
       <c r="D181" s="5"/>
       <c r="E181" s="5"/>
@@ -11433,8 +11905,10 @@
       <c r="AU181" s="5"/>
       <c r="AV181" s="5"/>
       <c r="AW181" s="5"/>
-    </row>
-    <row r="182" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX181" s="5"/>
+      <c r="AY181" s="5"/>
+    </row>
+    <row r="182" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C182" s="5"/>
       <c r="D182" s="5"/>
       <c r="E182" s="5"/>
@@ -11482,8 +11956,10 @@
       <c r="AU182" s="5"/>
       <c r="AV182" s="5"/>
       <c r="AW182" s="5"/>
-    </row>
-    <row r="183" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX182" s="5"/>
+      <c r="AY182" s="5"/>
+    </row>
+    <row r="183" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C183" s="5"/>
       <c r="D183" s="5"/>
       <c r="E183" s="5"/>
@@ -11531,8 +12007,10 @@
       <c r="AU183" s="5"/>
       <c r="AV183" s="5"/>
       <c r="AW183" s="5"/>
-    </row>
-    <row r="184" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX183" s="5"/>
+      <c r="AY183" s="5"/>
+    </row>
+    <row r="184" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C184" s="5"/>
       <c r="D184" s="5"/>
       <c r="E184" s="5"/>
@@ -11580,8 +12058,10 @@
       <c r="AU184" s="5"/>
       <c r="AV184" s="5"/>
       <c r="AW184" s="5"/>
-    </row>
-    <row r="185" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX184" s="5"/>
+      <c r="AY184" s="5"/>
+    </row>
+    <row r="185" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C185" s="5"/>
       <c r="D185" s="5"/>
       <c r="E185" s="5"/>
@@ -11629,8 +12109,10 @@
       <c r="AU185" s="5"/>
       <c r="AV185" s="5"/>
       <c r="AW185" s="5"/>
-    </row>
-    <row r="186" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX185" s="5"/>
+      <c r="AY185" s="5"/>
+    </row>
+    <row r="186" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C186" s="5"/>
       <c r="D186" s="5"/>
       <c r="E186" s="5"/>
@@ -11678,8 +12160,10 @@
       <c r="AU186" s="5"/>
       <c r="AV186" s="5"/>
       <c r="AW186" s="5"/>
-    </row>
-    <row r="187" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX186" s="5"/>
+      <c r="AY186" s="5"/>
+    </row>
+    <row r="187" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C187" s="5"/>
       <c r="D187" s="5"/>
       <c r="E187" s="5"/>
@@ -11727,8 +12211,10 @@
       <c r="AU187" s="5"/>
       <c r="AV187" s="5"/>
       <c r="AW187" s="5"/>
-    </row>
-    <row r="188" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX187" s="5"/>
+      <c r="AY187" s="5"/>
+    </row>
+    <row r="188" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C188" s="5"/>
       <c r="D188" s="5"/>
       <c r="E188" s="5"/>
@@ -11776,8 +12262,10 @@
       <c r="AU188" s="5"/>
       <c r="AV188" s="5"/>
       <c r="AW188" s="5"/>
-    </row>
-    <row r="189" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX188" s="5"/>
+      <c r="AY188" s="5"/>
+    </row>
+    <row r="189" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C189" s="5"/>
       <c r="D189" s="5"/>
       <c r="E189" s="5"/>
@@ -11825,8 +12313,10 @@
       <c r="AU189" s="5"/>
       <c r="AV189" s="5"/>
       <c r="AW189" s="5"/>
-    </row>
-    <row r="190" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX189" s="5"/>
+      <c r="AY189" s="5"/>
+    </row>
+    <row r="190" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C190" s="5"/>
       <c r="D190" s="5"/>
       <c r="E190" s="5"/>
@@ -11874,8 +12364,10 @@
       <c r="AU190" s="5"/>
       <c r="AV190" s="5"/>
       <c r="AW190" s="5"/>
-    </row>
-    <row r="191" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX190" s="5"/>
+      <c r="AY190" s="5"/>
+    </row>
+    <row r="191" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C191" s="5"/>
       <c r="D191" s="5"/>
       <c r="E191" s="5"/>
@@ -11923,8 +12415,10 @@
       <c r="AU191" s="5"/>
       <c r="AV191" s="5"/>
       <c r="AW191" s="5"/>
-    </row>
-    <row r="192" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX191" s="5"/>
+      <c r="AY191" s="5"/>
+    </row>
+    <row r="192" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C192" s="5"/>
       <c r="D192" s="5"/>
       <c r="E192" s="5"/>
@@ -11972,8 +12466,10 @@
       <c r="AU192" s="5"/>
       <c r="AV192" s="5"/>
       <c r="AW192" s="5"/>
-    </row>
-    <row r="193" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX192" s="5"/>
+      <c r="AY192" s="5"/>
+    </row>
+    <row r="193" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C193" s="5"/>
       <c r="D193" s="5"/>
       <c r="E193" s="5"/>
@@ -12021,8 +12517,10 @@
       <c r="AU193" s="5"/>
       <c r="AV193" s="5"/>
       <c r="AW193" s="5"/>
-    </row>
-    <row r="194" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX193" s="5"/>
+      <c r="AY193" s="5"/>
+    </row>
+    <row r="194" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C194" s="5"/>
       <c r="D194" s="5"/>
       <c r="E194" s="5"/>
@@ -12070,8 +12568,10 @@
       <c r="AU194" s="5"/>
       <c r="AV194" s="5"/>
       <c r="AW194" s="5"/>
-    </row>
-    <row r="195" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX194" s="5"/>
+      <c r="AY194" s="5"/>
+    </row>
+    <row r="195" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C195" s="5"/>
       <c r="D195" s="5"/>
       <c r="E195" s="5"/>
@@ -12119,8 +12619,10 @@
       <c r="AU195" s="5"/>
       <c r="AV195" s="5"/>
       <c r="AW195" s="5"/>
-    </row>
-    <row r="196" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX195" s="5"/>
+      <c r="AY195" s="5"/>
+    </row>
+    <row r="196" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C196" s="5"/>
       <c r="D196" s="5"/>
       <c r="E196" s="5"/>
@@ -12168,8 +12670,10 @@
       <c r="AU196" s="5"/>
       <c r="AV196" s="5"/>
       <c r="AW196" s="5"/>
-    </row>
-    <row r="197" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX196" s="5"/>
+      <c r="AY196" s="5"/>
+    </row>
+    <row r="197" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C197" s="5"/>
       <c r="D197" s="5"/>
       <c r="E197" s="5"/>
@@ -12217,8 +12721,10 @@
       <c r="AU197" s="5"/>
       <c r="AV197" s="5"/>
       <c r="AW197" s="5"/>
-    </row>
-    <row r="198" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX197" s="5"/>
+      <c r="AY197" s="5"/>
+    </row>
+    <row r="198" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C198" s="5"/>
       <c r="D198" s="5"/>
       <c r="E198" s="5"/>
@@ -12266,8 +12772,10 @@
       <c r="AU198" s="5"/>
       <c r="AV198" s="5"/>
       <c r="AW198" s="5"/>
-    </row>
-    <row r="199" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX198" s="5"/>
+      <c r="AY198" s="5"/>
+    </row>
+    <row r="199" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C199" s="5"/>
       <c r="D199" s="5"/>
       <c r="E199" s="5"/>
@@ -12315,8 +12823,10 @@
       <c r="AU199" s="5"/>
       <c r="AV199" s="5"/>
       <c r="AW199" s="5"/>
-    </row>
-    <row r="200" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX199" s="5"/>
+      <c r="AY199" s="5"/>
+    </row>
+    <row r="200" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C200" s="5"/>
       <c r="D200" s="5"/>
       <c r="E200" s="5"/>
@@ -12364,8 +12874,10 @@
       <c r="AU200" s="5"/>
       <c r="AV200" s="5"/>
       <c r="AW200" s="5"/>
-    </row>
-    <row r="201" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX200" s="5"/>
+      <c r="AY200" s="5"/>
+    </row>
+    <row r="201" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C201" s="5"/>
       <c r="D201" s="5"/>
       <c r="E201" s="5"/>
@@ -12413,8 +12925,10 @@
       <c r="AU201" s="5"/>
       <c r="AV201" s="5"/>
       <c r="AW201" s="5"/>
-    </row>
-    <row r="202" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX201" s="5"/>
+      <c r="AY201" s="5"/>
+    </row>
+    <row r="202" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C202" s="5"/>
       <c r="D202" s="5"/>
       <c r="E202" s="5"/>
@@ -12462,8 +12976,10 @@
       <c r="AU202" s="5"/>
       <c r="AV202" s="5"/>
       <c r="AW202" s="5"/>
-    </row>
-    <row r="203" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX202" s="5"/>
+      <c r="AY202" s="5"/>
+    </row>
+    <row r="203" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C203" s="5"/>
       <c r="D203" s="5"/>
       <c r="E203" s="5"/>
@@ -12511,8 +13027,10 @@
       <c r="AU203" s="5"/>
       <c r="AV203" s="5"/>
       <c r="AW203" s="5"/>
-    </row>
-    <row r="204" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX203" s="5"/>
+      <c r="AY203" s="5"/>
+    </row>
+    <row r="204" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C204" s="5"/>
       <c r="D204" s="5"/>
       <c r="E204" s="5"/>
@@ -12560,8 +13078,10 @@
       <c r="AU204" s="5"/>
       <c r="AV204" s="5"/>
       <c r="AW204" s="5"/>
-    </row>
-    <row r="205" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX204" s="5"/>
+      <c r="AY204" s="5"/>
+    </row>
+    <row r="205" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C205" s="5"/>
       <c r="D205" s="5"/>
       <c r="E205" s="5"/>
@@ -12609,8 +13129,10 @@
       <c r="AU205" s="5"/>
       <c r="AV205" s="5"/>
       <c r="AW205" s="5"/>
-    </row>
-    <row r="206" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX205" s="5"/>
+      <c r="AY205" s="5"/>
+    </row>
+    <row r="206" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C206" s="5"/>
       <c r="D206" s="5"/>
       <c r="E206" s="5"/>
@@ -12658,8 +13180,10 @@
       <c r="AU206" s="5"/>
       <c r="AV206" s="5"/>
       <c r="AW206" s="5"/>
-    </row>
-    <row r="207" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX206" s="5"/>
+      <c r="AY206" s="5"/>
+    </row>
+    <row r="207" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C207" s="5"/>
       <c r="D207" s="5"/>
       <c r="E207" s="5"/>
@@ -12707,8 +13231,10 @@
       <c r="AU207" s="5"/>
       <c r="AV207" s="5"/>
       <c r="AW207" s="5"/>
-    </row>
-    <row r="208" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX207" s="5"/>
+      <c r="AY207" s="5"/>
+    </row>
+    <row r="208" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C208" s="5"/>
       <c r="D208" s="5"/>
       <c r="E208" s="5"/>
@@ -12756,8 +13282,10 @@
       <c r="AU208" s="5"/>
       <c r="AV208" s="5"/>
       <c r="AW208" s="5"/>
-    </row>
-    <row r="209" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX208" s="5"/>
+      <c r="AY208" s="5"/>
+    </row>
+    <row r="209" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C209" s="5"/>
       <c r="D209" s="5"/>
       <c r="E209" s="5"/>
@@ -12805,8 +13333,10 @@
       <c r="AU209" s="5"/>
       <c r="AV209" s="5"/>
       <c r="AW209" s="5"/>
-    </row>
-    <row r="210" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX209" s="5"/>
+      <c r="AY209" s="5"/>
+    </row>
+    <row r="210" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C210" s="5"/>
       <c r="D210" s="5"/>
       <c r="E210" s="5"/>
@@ -12854,8 +13384,10 @@
       <c r="AU210" s="5"/>
       <c r="AV210" s="5"/>
       <c r="AW210" s="5"/>
-    </row>
-    <row r="211" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX210" s="5"/>
+      <c r="AY210" s="5"/>
+    </row>
+    <row r="211" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C211" s="5"/>
       <c r="D211" s="5"/>
       <c r="E211" s="5"/>
@@ -12903,8 +13435,10 @@
       <c r="AU211" s="5"/>
       <c r="AV211" s="5"/>
       <c r="AW211" s="5"/>
-    </row>
-    <row r="212" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX211" s="5"/>
+      <c r="AY211" s="5"/>
+    </row>
+    <row r="212" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C212" s="5"/>
       <c r="D212" s="5"/>
       <c r="E212" s="5"/>
@@ -12952,8 +13486,10 @@
       <c r="AU212" s="5"/>
       <c r="AV212" s="5"/>
       <c r="AW212" s="5"/>
-    </row>
-    <row r="213" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX212" s="5"/>
+      <c r="AY212" s="5"/>
+    </row>
+    <row r="213" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C213" s="5"/>
       <c r="D213" s="5"/>
       <c r="E213" s="5"/>
@@ -13001,8 +13537,10 @@
       <c r="AU213" s="5"/>
       <c r="AV213" s="5"/>
       <c r="AW213" s="5"/>
-    </row>
-    <row r="214" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX213" s="5"/>
+      <c r="AY213" s="5"/>
+    </row>
+    <row r="214" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C214" s="5"/>
       <c r="D214" s="5"/>
       <c r="E214" s="5"/>
@@ -13050,8 +13588,10 @@
       <c r="AU214" s="5"/>
       <c r="AV214" s="5"/>
       <c r="AW214" s="5"/>
-    </row>
-    <row r="215" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX214" s="5"/>
+      <c r="AY214" s="5"/>
+    </row>
+    <row r="215" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C215" s="5"/>
       <c r="D215" s="5"/>
       <c r="E215" s="5"/>
@@ -13099,8 +13639,10 @@
       <c r="AU215" s="5"/>
       <c r="AV215" s="5"/>
       <c r="AW215" s="5"/>
-    </row>
-    <row r="216" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX215" s="5"/>
+      <c r="AY215" s="5"/>
+    </row>
+    <row r="216" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C216" s="5"/>
       <c r="D216" s="5"/>
       <c r="E216" s="5"/>
@@ -13148,8 +13690,10 @@
       <c r="AU216" s="5"/>
       <c r="AV216" s="5"/>
       <c r="AW216" s="5"/>
-    </row>
-    <row r="217" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX216" s="5"/>
+      <c r="AY216" s="5"/>
+    </row>
+    <row r="217" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C217" s="5"/>
       <c r="D217" s="5"/>
       <c r="E217" s="5"/>
@@ -13197,8 +13741,10 @@
       <c r="AU217" s="5"/>
       <c r="AV217" s="5"/>
       <c r="AW217" s="5"/>
-    </row>
-    <row r="218" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX217" s="5"/>
+      <c r="AY217" s="5"/>
+    </row>
+    <row r="218" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C218" s="5"/>
       <c r="D218" s="5"/>
       <c r="E218" s="5"/>
@@ -13246,8 +13792,10 @@
       <c r="AU218" s="5"/>
       <c r="AV218" s="5"/>
       <c r="AW218" s="5"/>
-    </row>
-    <row r="219" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX218" s="5"/>
+      <c r="AY218" s="5"/>
+    </row>
+    <row r="219" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C219" s="5"/>
       <c r="D219" s="5"/>
       <c r="E219" s="5"/>
@@ -13295,8 +13843,10 @@
       <c r="AU219" s="5"/>
       <c r="AV219" s="5"/>
       <c r="AW219" s="5"/>
-    </row>
-    <row r="220" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX219" s="5"/>
+      <c r="AY219" s="5"/>
+    </row>
+    <row r="220" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C220" s="5"/>
       <c r="D220" s="5"/>
       <c r="E220" s="5"/>
@@ -13344,8 +13894,10 @@
       <c r="AU220" s="5"/>
       <c r="AV220" s="5"/>
       <c r="AW220" s="5"/>
-    </row>
-    <row r="221" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX220" s="5"/>
+      <c r="AY220" s="5"/>
+    </row>
+    <row r="221" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C221" s="5"/>
       <c r="D221" s="5"/>
       <c r="E221" s="5"/>
@@ -13393,8 +13945,10 @@
       <c r="AU221" s="5"/>
       <c r="AV221" s="5"/>
       <c r="AW221" s="5"/>
-    </row>
-    <row r="222" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX221" s="5"/>
+      <c r="AY221" s="5"/>
+    </row>
+    <row r="222" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C222" s="5"/>
       <c r="D222" s="5"/>
       <c r="E222" s="5"/>
@@ -13442,8 +13996,10 @@
       <c r="AU222" s="5"/>
       <c r="AV222" s="5"/>
       <c r="AW222" s="5"/>
-    </row>
-    <row r="223" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX222" s="5"/>
+      <c r="AY222" s="5"/>
+    </row>
+    <row r="223" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C223" s="5"/>
       <c r="D223" s="5"/>
       <c r="E223" s="5"/>
@@ -13491,8 +14047,10 @@
       <c r="AU223" s="5"/>
       <c r="AV223" s="5"/>
       <c r="AW223" s="5"/>
-    </row>
-    <row r="224" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX223" s="5"/>
+      <c r="AY223" s="5"/>
+    </row>
+    <row r="224" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C224" s="5"/>
       <c r="D224" s="5"/>
       <c r="E224" s="5"/>
@@ -13540,8 +14098,10 @@
       <c r="AU224" s="5"/>
       <c r="AV224" s="5"/>
       <c r="AW224" s="5"/>
-    </row>
-    <row r="225" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX224" s="5"/>
+      <c r="AY224" s="5"/>
+    </row>
+    <row r="225" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C225" s="5"/>
       <c r="D225" s="5"/>
       <c r="E225" s="5"/>
@@ -13589,8 +14149,10 @@
       <c r="AU225" s="5"/>
       <c r="AV225" s="5"/>
       <c r="AW225" s="5"/>
-    </row>
-    <row r="226" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX225" s="5"/>
+      <c r="AY225" s="5"/>
+    </row>
+    <row r="226" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C226" s="5"/>
       <c r="D226" s="5"/>
       <c r="E226" s="5"/>
@@ -13638,8 +14200,10 @@
       <c r="AU226" s="5"/>
       <c r="AV226" s="5"/>
       <c r="AW226" s="5"/>
-    </row>
-    <row r="227" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX226" s="5"/>
+      <c r="AY226" s="5"/>
+    </row>
+    <row r="227" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C227" s="5"/>
       <c r="D227" s="5"/>
       <c r="E227" s="5"/>
@@ -13687,8 +14251,10 @@
       <c r="AU227" s="5"/>
       <c r="AV227" s="5"/>
       <c r="AW227" s="5"/>
-    </row>
-    <row r="228" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX227" s="5"/>
+      <c r="AY227" s="5"/>
+    </row>
+    <row r="228" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C228" s="5"/>
       <c r="D228" s="5"/>
       <c r="E228" s="5"/>
@@ -13736,8 +14302,10 @@
       <c r="AU228" s="5"/>
       <c r="AV228" s="5"/>
       <c r="AW228" s="5"/>
-    </row>
-    <row r="229" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX228" s="5"/>
+      <c r="AY228" s="5"/>
+    </row>
+    <row r="229" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C229" s="5"/>
       <c r="D229" s="5"/>
       <c r="E229" s="5"/>
@@ -13785,8 +14353,10 @@
       <c r="AU229" s="5"/>
       <c r="AV229" s="5"/>
       <c r="AW229" s="5"/>
-    </row>
-    <row r="230" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX229" s="5"/>
+      <c r="AY229" s="5"/>
+    </row>
+    <row r="230" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C230" s="5"/>
       <c r="D230" s="5"/>
       <c r="E230" s="5"/>
@@ -13834,8 +14404,10 @@
       <c r="AU230" s="5"/>
       <c r="AV230" s="5"/>
       <c r="AW230" s="5"/>
-    </row>
-    <row r="231" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX230" s="5"/>
+      <c r="AY230" s="5"/>
+    </row>
+    <row r="231" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C231" s="5"/>
       <c r="D231" s="5"/>
       <c r="E231" s="5"/>
@@ -13883,8 +14455,10 @@
       <c r="AU231" s="5"/>
       <c r="AV231" s="5"/>
       <c r="AW231" s="5"/>
-    </row>
-    <row r="232" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX231" s="5"/>
+      <c r="AY231" s="5"/>
+    </row>
+    <row r="232" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C232" s="5"/>
       <c r="D232" s="5"/>
       <c r="E232" s="5"/>
@@ -13932,8 +14506,10 @@
       <c r="AU232" s="5"/>
       <c r="AV232" s="5"/>
       <c r="AW232" s="5"/>
-    </row>
-    <row r="233" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX232" s="5"/>
+      <c r="AY232" s="5"/>
+    </row>
+    <row r="233" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C233" s="5"/>
       <c r="D233" s="5"/>
       <c r="E233" s="5"/>
@@ -13981,8 +14557,10 @@
       <c r="AU233" s="5"/>
       <c r="AV233" s="5"/>
       <c r="AW233" s="5"/>
-    </row>
-    <row r="234" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX233" s="5"/>
+      <c r="AY233" s="5"/>
+    </row>
+    <row r="234" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C234" s="5"/>
       <c r="D234" s="5"/>
       <c r="E234" s="5"/>
@@ -14030,8 +14608,10 @@
       <c r="AU234" s="5"/>
       <c r="AV234" s="5"/>
       <c r="AW234" s="5"/>
-    </row>
-    <row r="235" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX234" s="5"/>
+      <c r="AY234" s="5"/>
+    </row>
+    <row r="235" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C235" s="5"/>
       <c r="D235" s="5"/>
       <c r="E235" s="5"/>
@@ -14077,8 +14657,10 @@
       <c r="AS235" s="5"/>
       <c r="AT235" s="5"/>
       <c r="AU235" s="5"/>
-    </row>
-    <row r="236" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AV235" s="5"/>
+      <c r="AW235" s="5"/>
+    </row>
+    <row r="236" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C236" s="5"/>
       <c r="D236" s="5"/>
       <c r="E236" s="5"/>
@@ -14124,8 +14706,10 @@
       <c r="AS236" s="5"/>
       <c r="AT236" s="5"/>
       <c r="AU236" s="5"/>
-    </row>
-    <row r="237" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AV236" s="5"/>
+      <c r="AW236" s="5"/>
+    </row>
+    <row r="237" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C237" s="5"/>
       <c r="D237" s="5"/>
       <c r="E237" s="5"/>
@@ -14171,8 +14755,10 @@
       <c r="AS237" s="5"/>
       <c r="AT237" s="5"/>
       <c r="AU237" s="5"/>
-    </row>
-    <row r="238" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AV237" s="5"/>
+      <c r="AW237" s="5"/>
+    </row>
+    <row r="238" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C238" s="5"/>
       <c r="D238" s="5"/>
       <c r="E238" s="5"/>
@@ -14218,8 +14804,10 @@
       <c r="AS238" s="5"/>
       <c r="AT238" s="5"/>
       <c r="AU238" s="5"/>
-    </row>
-    <row r="239" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AV238" s="5"/>
+      <c r="AW238" s="5"/>
+    </row>
+    <row r="239" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C239" s="5"/>
       <c r="D239" s="5"/>
       <c r="E239" s="5"/>
@@ -14265,8 +14853,10 @@
       <c r="AS239" s="5"/>
       <c r="AT239" s="5"/>
       <c r="AU239" s="5"/>
-    </row>
-    <row r="240" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AV239" s="5"/>
+      <c r="AW239" s="5"/>
+    </row>
+    <row r="240" spans="3:51" x14ac:dyDescent="0.2">
       <c r="C240" s="5"/>
       <c r="D240" s="5"/>
       <c r="E240" s="5"/>
@@ -14312,8 +14902,10 @@
       <c r="AS240" s="5"/>
       <c r="AT240" s="5"/>
       <c r="AU240" s="5"/>
-    </row>
-    <row r="241" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV240" s="5"/>
+      <c r="AW240" s="5"/>
+    </row>
+    <row r="241" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C241" s="5"/>
       <c r="D241" s="5"/>
       <c r="E241" s="5"/>
@@ -14359,8 +14951,10 @@
       <c r="AS241" s="5"/>
       <c r="AT241" s="5"/>
       <c r="AU241" s="5"/>
-    </row>
-    <row r="242" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV241" s="5"/>
+      <c r="AW241" s="5"/>
+    </row>
+    <row r="242" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C242" s="5"/>
       <c r="D242" s="5"/>
       <c r="E242" s="5"/>
@@ -14406,8 +15000,10 @@
       <c r="AS242" s="5"/>
       <c r="AT242" s="5"/>
       <c r="AU242" s="5"/>
-    </row>
-    <row r="243" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV242" s="5"/>
+      <c r="AW242" s="5"/>
+    </row>
+    <row r="243" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C243" s="5"/>
       <c r="D243" s="5"/>
       <c r="E243" s="5"/>
@@ -14453,8 +15049,10 @@
       <c r="AS243" s="5"/>
       <c r="AT243" s="5"/>
       <c r="AU243" s="5"/>
-    </row>
-    <row r="244" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV243" s="5"/>
+      <c r="AW243" s="5"/>
+    </row>
+    <row r="244" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C244" s="5"/>
       <c r="D244" s="5"/>
       <c r="E244" s="5"/>
@@ -14500,8 +15098,10 @@
       <c r="AS244" s="5"/>
       <c r="AT244" s="5"/>
       <c r="AU244" s="5"/>
-    </row>
-    <row r="245" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV244" s="5"/>
+      <c r="AW244" s="5"/>
+    </row>
+    <row r="245" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C245" s="5"/>
       <c r="D245" s="5"/>
       <c r="E245" s="5"/>
@@ -14547,8 +15147,10 @@
       <c r="AS245" s="5"/>
       <c r="AT245" s="5"/>
       <c r="AU245" s="5"/>
-    </row>
-    <row r="246" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV245" s="5"/>
+      <c r="AW245" s="5"/>
+    </row>
+    <row r="246" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C246" s="5"/>
       <c r="D246" s="5"/>
       <c r="E246" s="5"/>
@@ -14594,8 +15196,10 @@
       <c r="AS246" s="5"/>
       <c r="AT246" s="5"/>
       <c r="AU246" s="5"/>
-    </row>
-    <row r="247" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV246" s="5"/>
+      <c r="AW246" s="5"/>
+    </row>
+    <row r="247" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C247" s="5"/>
       <c r="D247" s="5"/>
       <c r="E247" s="5"/>
@@ -14641,8 +15245,10 @@
       <c r="AS247" s="5"/>
       <c r="AT247" s="5"/>
       <c r="AU247" s="5"/>
-    </row>
-    <row r="248" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV247" s="5"/>
+      <c r="AW247" s="5"/>
+    </row>
+    <row r="248" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C248" s="5"/>
       <c r="D248" s="5"/>
       <c r="E248" s="5"/>
@@ -14688,8 +15294,10 @@
       <c r="AS248" s="5"/>
       <c r="AT248" s="5"/>
       <c r="AU248" s="5"/>
-    </row>
-    <row r="249" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV248" s="5"/>
+      <c r="AW248" s="5"/>
+    </row>
+    <row r="249" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C249" s="5"/>
       <c r="D249" s="5"/>
       <c r="E249" s="5"/>
@@ -14735,8 +15343,10 @@
       <c r="AS249" s="5"/>
       <c r="AT249" s="5"/>
       <c r="AU249" s="5"/>
-    </row>
-    <row r="250" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV249" s="5"/>
+      <c r="AW249" s="5"/>
+    </row>
+    <row r="250" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C250" s="5"/>
       <c r="D250" s="5"/>
       <c r="E250" s="5"/>
@@ -14782,8 +15392,10 @@
       <c r="AS250" s="5"/>
       <c r="AT250" s="5"/>
       <c r="AU250" s="5"/>
-    </row>
-    <row r="251" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV250" s="5"/>
+      <c r="AW250" s="5"/>
+    </row>
+    <row r="251" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C251" s="5"/>
       <c r="D251" s="5"/>
       <c r="E251" s="5"/>
@@ -14829,8 +15441,10 @@
       <c r="AS251" s="5"/>
       <c r="AT251" s="5"/>
       <c r="AU251" s="5"/>
-    </row>
-    <row r="252" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV251" s="5"/>
+      <c r="AW251" s="5"/>
+    </row>
+    <row r="252" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C252" s="5"/>
       <c r="D252" s="5"/>
       <c r="E252" s="5"/>
@@ -14876,8 +15490,10 @@
       <c r="AS252" s="5"/>
       <c r="AT252" s="5"/>
       <c r="AU252" s="5"/>
-    </row>
-    <row r="253" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV252" s="5"/>
+      <c r="AW252" s="5"/>
+    </row>
+    <row r="253" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C253" s="5"/>
       <c r="D253" s="5"/>
       <c r="E253" s="5"/>
@@ -14923,8 +15539,10 @@
       <c r="AS253" s="5"/>
       <c r="AT253" s="5"/>
       <c r="AU253" s="5"/>
-    </row>
-    <row r="254" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV253" s="5"/>
+      <c r="AW253" s="5"/>
+    </row>
+    <row r="254" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C254" s="5"/>
       <c r="D254" s="5"/>
       <c r="E254" s="5"/>
@@ -14970,8 +15588,10 @@
       <c r="AS254" s="5"/>
       <c r="AT254" s="5"/>
       <c r="AU254" s="5"/>
-    </row>
-    <row r="255" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV254" s="5"/>
+      <c r="AW254" s="5"/>
+    </row>
+    <row r="255" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C255" s="5"/>
       <c r="D255" s="5"/>
       <c r="E255" s="5"/>
@@ -15017,8 +15637,10 @@
       <c r="AS255" s="5"/>
       <c r="AT255" s="5"/>
       <c r="AU255" s="5"/>
-    </row>
-    <row r="256" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV255" s="5"/>
+      <c r="AW255" s="5"/>
+    </row>
+    <row r="256" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C256" s="5"/>
       <c r="D256" s="5"/>
       <c r="E256" s="5"/>
@@ -15064,8 +15686,10 @@
       <c r="AS256" s="5"/>
       <c r="AT256" s="5"/>
       <c r="AU256" s="5"/>
-    </row>
-    <row r="257" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV256" s="5"/>
+      <c r="AW256" s="5"/>
+    </row>
+    <row r="257" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C257" s="5"/>
       <c r="D257" s="5"/>
       <c r="E257" s="5"/>
@@ -15111,8 +15735,10 @@
       <c r="AS257" s="5"/>
       <c r="AT257" s="5"/>
       <c r="AU257" s="5"/>
-    </row>
-    <row r="258" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV257" s="5"/>
+      <c r="AW257" s="5"/>
+    </row>
+    <row r="258" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C258" s="5"/>
       <c r="D258" s="5"/>
       <c r="E258" s="5"/>
@@ -15158,8 +15784,10 @@
       <c r="AS258" s="5"/>
       <c r="AT258" s="5"/>
       <c r="AU258" s="5"/>
-    </row>
-    <row r="259" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV258" s="5"/>
+      <c r="AW258" s="5"/>
+    </row>
+    <row r="259" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C259" s="5"/>
       <c r="D259" s="5"/>
       <c r="E259" s="5"/>
@@ -15205,8 +15833,10 @@
       <c r="AS259" s="5"/>
       <c r="AT259" s="5"/>
       <c r="AU259" s="5"/>
-    </row>
-    <row r="260" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV259" s="5"/>
+      <c r="AW259" s="5"/>
+    </row>
+    <row r="260" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C260" s="5"/>
       <c r="D260" s="5"/>
       <c r="E260" s="5"/>
@@ -15252,8 +15882,10 @@
       <c r="AS260" s="5"/>
       <c r="AT260" s="5"/>
       <c r="AU260" s="5"/>
-    </row>
-    <row r="261" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV260" s="5"/>
+      <c r="AW260" s="5"/>
+    </row>
+    <row r="261" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C261" s="5"/>
       <c r="D261" s="5"/>
       <c r="E261" s="5"/>
@@ -15299,8 +15931,10 @@
       <c r="AS261" s="5"/>
       <c r="AT261" s="5"/>
       <c r="AU261" s="5"/>
-    </row>
-    <row r="262" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV261" s="5"/>
+      <c r="AW261" s="5"/>
+    </row>
+    <row r="262" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C262" s="5"/>
       <c r="D262" s="5"/>
       <c r="E262" s="5"/>
@@ -15346,8 +15980,10 @@
       <c r="AS262" s="5"/>
       <c r="AT262" s="5"/>
       <c r="AU262" s="5"/>
-    </row>
-    <row r="263" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV262" s="5"/>
+      <c r="AW262" s="5"/>
+    </row>
+    <row r="263" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C263" s="5"/>
       <c r="D263" s="5"/>
       <c r="E263" s="5"/>
@@ -15393,8 +16029,10 @@
       <c r="AS263" s="5"/>
       <c r="AT263" s="5"/>
       <c r="AU263" s="5"/>
-    </row>
-    <row r="264" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV263" s="5"/>
+      <c r="AW263" s="5"/>
+    </row>
+    <row r="264" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C264" s="5"/>
       <c r="D264" s="5"/>
       <c r="E264" s="5"/>
@@ -15440,8 +16078,10 @@
       <c r="AS264" s="5"/>
       <c r="AT264" s="5"/>
       <c r="AU264" s="5"/>
-    </row>
-    <row r="265" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV264" s="5"/>
+      <c r="AW264" s="5"/>
+    </row>
+    <row r="265" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C265" s="5"/>
       <c r="D265" s="5"/>
       <c r="E265" s="5"/>
@@ -15487,8 +16127,10 @@
       <c r="AS265" s="5"/>
       <c r="AT265" s="5"/>
       <c r="AU265" s="5"/>
-    </row>
-    <row r="266" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV265" s="5"/>
+      <c r="AW265" s="5"/>
+    </row>
+    <row r="266" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C266" s="5"/>
       <c r="D266" s="5"/>
       <c r="E266" s="5"/>
@@ -15534,8 +16176,10 @@
       <c r="AS266" s="5"/>
       <c r="AT266" s="5"/>
       <c r="AU266" s="5"/>
-    </row>
-    <row r="267" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV266" s="5"/>
+      <c r="AW266" s="5"/>
+    </row>
+    <row r="267" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C267" s="5"/>
       <c r="D267" s="5"/>
       <c r="E267" s="5"/>
@@ -15581,8 +16225,10 @@
       <c r="AS267" s="5"/>
       <c r="AT267" s="5"/>
       <c r="AU267" s="5"/>
-    </row>
-    <row r="268" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV267" s="5"/>
+      <c r="AW267" s="5"/>
+    </row>
+    <row r="268" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C268" s="5"/>
       <c r="D268" s="5"/>
       <c r="E268" s="5"/>
@@ -15628,8 +16274,10 @@
       <c r="AS268" s="5"/>
       <c r="AT268" s="5"/>
       <c r="AU268" s="5"/>
-    </row>
-    <row r="269" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV268" s="5"/>
+      <c r="AW268" s="5"/>
+    </row>
+    <row r="269" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C269" s="5"/>
       <c r="D269" s="5"/>
       <c r="E269" s="5"/>
@@ -15675,8 +16323,10 @@
       <c r="AS269" s="5"/>
       <c r="AT269" s="5"/>
       <c r="AU269" s="5"/>
-    </row>
-    <row r="270" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV269" s="5"/>
+      <c r="AW269" s="5"/>
+    </row>
+    <row r="270" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C270" s="5"/>
       <c r="D270" s="5"/>
       <c r="E270" s="5"/>
@@ -15722,8 +16372,10 @@
       <c r="AS270" s="5"/>
       <c r="AT270" s="5"/>
       <c r="AU270" s="5"/>
-    </row>
-    <row r="271" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV270" s="5"/>
+      <c r="AW270" s="5"/>
+    </row>
+    <row r="271" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C271" s="5"/>
       <c r="D271" s="5"/>
       <c r="E271" s="5"/>
@@ -15769,8 +16421,10 @@
       <c r="AS271" s="5"/>
       <c r="AT271" s="5"/>
       <c r="AU271" s="5"/>
-    </row>
-    <row r="272" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV271" s="5"/>
+      <c r="AW271" s="5"/>
+    </row>
+    <row r="272" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C272" s="5"/>
       <c r="D272" s="5"/>
       <c r="E272" s="5"/>
@@ -15816,8 +16470,10 @@
       <c r="AS272" s="5"/>
       <c r="AT272" s="5"/>
       <c r="AU272" s="5"/>
-    </row>
-    <row r="273" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV272" s="5"/>
+      <c r="AW272" s="5"/>
+    </row>
+    <row r="273" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C273" s="5"/>
       <c r="D273" s="5"/>
       <c r="E273" s="5"/>
@@ -15863,8 +16519,10 @@
       <c r="AS273" s="5"/>
       <c r="AT273" s="5"/>
       <c r="AU273" s="5"/>
-    </row>
-    <row r="274" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV273" s="5"/>
+      <c r="AW273" s="5"/>
+    </row>
+    <row r="274" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C274" s="5"/>
       <c r="D274" s="5"/>
       <c r="E274" s="5"/>
@@ -15910,8 +16568,10 @@
       <c r="AS274" s="5"/>
       <c r="AT274" s="5"/>
       <c r="AU274" s="5"/>
-    </row>
-    <row r="275" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV274" s="5"/>
+      <c r="AW274" s="5"/>
+    </row>
+    <row r="275" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C275" s="5"/>
       <c r="D275" s="5"/>
       <c r="E275" s="5"/>
@@ -15957,8 +16617,10 @@
       <c r="AS275" s="5"/>
       <c r="AT275" s="5"/>
       <c r="AU275" s="5"/>
-    </row>
-    <row r="276" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV275" s="5"/>
+      <c r="AW275" s="5"/>
+    </row>
+    <row r="276" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C276" s="5"/>
       <c r="D276" s="5"/>
       <c r="E276" s="5"/>
@@ -16004,8 +16666,10 @@
       <c r="AS276" s="5"/>
       <c r="AT276" s="5"/>
       <c r="AU276" s="5"/>
-    </row>
-    <row r="277" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV276" s="5"/>
+      <c r="AW276" s="5"/>
+    </row>
+    <row r="277" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C277" s="5"/>
       <c r="D277" s="5"/>
       <c r="E277" s="5"/>
@@ -16051,8 +16715,10 @@
       <c r="AS277" s="5"/>
       <c r="AT277" s="5"/>
       <c r="AU277" s="5"/>
-    </row>
-    <row r="278" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV277" s="5"/>
+      <c r="AW277" s="5"/>
+    </row>
+    <row r="278" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C278" s="5"/>
       <c r="D278" s="5"/>
       <c r="E278" s="5"/>
@@ -16098,8 +16764,10 @@
       <c r="AS278" s="5"/>
       <c r="AT278" s="5"/>
       <c r="AU278" s="5"/>
-    </row>
-    <row r="279" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV278" s="5"/>
+      <c r="AW278" s="5"/>
+    </row>
+    <row r="279" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C279" s="5"/>
       <c r="D279" s="5"/>
       <c r="E279" s="5"/>
@@ -16145,8 +16813,10 @@
       <c r="AS279" s="5"/>
       <c r="AT279" s="5"/>
       <c r="AU279" s="5"/>
-    </row>
-    <row r="280" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV279" s="5"/>
+      <c r="AW279" s="5"/>
+    </row>
+    <row r="280" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C280" s="5"/>
       <c r="D280" s="5"/>
       <c r="E280" s="5"/>
@@ -16192,8 +16862,10 @@
       <c r="AS280" s="5"/>
       <c r="AT280" s="5"/>
       <c r="AU280" s="5"/>
-    </row>
-    <row r="281" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV280" s="5"/>
+      <c r="AW280" s="5"/>
+    </row>
+    <row r="281" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C281" s="5"/>
       <c r="D281" s="5"/>
       <c r="E281" s="5"/>
@@ -16239,8 +16911,10 @@
       <c r="AS281" s="5"/>
       <c r="AT281" s="5"/>
       <c r="AU281" s="5"/>
-    </row>
-    <row r="282" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV281" s="5"/>
+      <c r="AW281" s="5"/>
+    </row>
+    <row r="282" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C282" s="5"/>
       <c r="D282" s="5"/>
       <c r="E282" s="5"/>
@@ -16286,8 +16960,10 @@
       <c r="AS282" s="5"/>
       <c r="AT282" s="5"/>
       <c r="AU282" s="5"/>
-    </row>
-    <row r="283" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV282" s="5"/>
+      <c r="AW282" s="5"/>
+    </row>
+    <row r="283" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C283" s="5"/>
       <c r="D283" s="5"/>
       <c r="E283" s="5"/>
@@ -16333,8 +17009,10 @@
       <c r="AS283" s="5"/>
       <c r="AT283" s="5"/>
       <c r="AU283" s="5"/>
-    </row>
-    <row r="284" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV283" s="5"/>
+      <c r="AW283" s="5"/>
+    </row>
+    <row r="284" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C284" s="5"/>
       <c r="D284" s="5"/>
       <c r="E284" s="5"/>
@@ -16380,8 +17058,10 @@
       <c r="AS284" s="5"/>
       <c r="AT284" s="5"/>
       <c r="AU284" s="5"/>
-    </row>
-    <row r="285" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV284" s="5"/>
+      <c r="AW284" s="5"/>
+    </row>
+    <row r="285" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C285" s="5"/>
       <c r="D285" s="5"/>
       <c r="E285" s="5"/>
@@ -16427,8 +17107,10 @@
       <c r="AS285" s="5"/>
       <c r="AT285" s="5"/>
       <c r="AU285" s="5"/>
-    </row>
-    <row r="286" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV285" s="5"/>
+      <c r="AW285" s="5"/>
+    </row>
+    <row r="286" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C286" s="5"/>
       <c r="D286" s="5"/>
       <c r="E286" s="5"/>
@@ -16474,8 +17156,10 @@
       <c r="AS286" s="5"/>
       <c r="AT286" s="5"/>
       <c r="AU286" s="5"/>
-    </row>
-    <row r="287" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV286" s="5"/>
+      <c r="AW286" s="5"/>
+    </row>
+    <row r="287" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C287" s="5"/>
       <c r="D287" s="5"/>
       <c r="E287" s="5"/>
@@ -16521,8 +17205,10 @@
       <c r="AS287" s="5"/>
       <c r="AT287" s="5"/>
       <c r="AU287" s="5"/>
-    </row>
-    <row r="288" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV287" s="5"/>
+      <c r="AW287" s="5"/>
+    </row>
+    <row r="288" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C288" s="5"/>
       <c r="D288" s="5"/>
       <c r="E288" s="5"/>
@@ -16568,8 +17254,10 @@
       <c r="AS288" s="5"/>
       <c r="AT288" s="5"/>
       <c r="AU288" s="5"/>
-    </row>
-    <row r="289" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV288" s="5"/>
+      <c r="AW288" s="5"/>
+    </row>
+    <row r="289" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C289" s="5"/>
       <c r="D289" s="5"/>
       <c r="E289" s="5"/>
@@ -16615,8 +17303,10 @@
       <c r="AS289" s="5"/>
       <c r="AT289" s="5"/>
       <c r="AU289" s="5"/>
-    </row>
-    <row r="290" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV289" s="5"/>
+      <c r="AW289" s="5"/>
+    </row>
+    <row r="290" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C290" s="5"/>
       <c r="D290" s="5"/>
       <c r="E290" s="5"/>
@@ -16662,8 +17352,10 @@
       <c r="AS290" s="5"/>
       <c r="AT290" s="5"/>
       <c r="AU290" s="5"/>
-    </row>
-    <row r="291" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV290" s="5"/>
+      <c r="AW290" s="5"/>
+    </row>
+    <row r="291" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C291" s="5"/>
       <c r="D291" s="5"/>
       <c r="E291" s="5"/>
@@ -16709,8 +17401,10 @@
       <c r="AS291" s="5"/>
       <c r="AT291" s="5"/>
       <c r="AU291" s="5"/>
-    </row>
-    <row r="292" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV291" s="5"/>
+      <c r="AW291" s="5"/>
+    </row>
+    <row r="292" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C292" s="5"/>
       <c r="D292" s="5"/>
       <c r="E292" s="5"/>
@@ -16756,8 +17450,10 @@
       <c r="AS292" s="5"/>
       <c r="AT292" s="5"/>
       <c r="AU292" s="5"/>
-    </row>
-    <row r="293" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV292" s="5"/>
+      <c r="AW292" s="5"/>
+    </row>
+    <row r="293" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C293" s="5"/>
       <c r="D293" s="5"/>
       <c r="E293" s="5"/>
@@ -16803,8 +17499,10 @@
       <c r="AS293" s="5"/>
       <c r="AT293" s="5"/>
       <c r="AU293" s="5"/>
-    </row>
-    <row r="294" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV293" s="5"/>
+      <c r="AW293" s="5"/>
+    </row>
+    <row r="294" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C294" s="5"/>
       <c r="D294" s="5"/>
       <c r="E294" s="5"/>
@@ -16850,8 +17548,10 @@
       <c r="AS294" s="5"/>
       <c r="AT294" s="5"/>
       <c r="AU294" s="5"/>
-    </row>
-    <row r="295" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV294" s="5"/>
+      <c r="AW294" s="5"/>
+    </row>
+    <row r="295" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C295" s="5"/>
       <c r="D295" s="5"/>
       <c r="E295" s="5"/>
@@ -16897,8 +17597,10 @@
       <c r="AS295" s="5"/>
       <c r="AT295" s="5"/>
       <c r="AU295" s="5"/>
-    </row>
-    <row r="296" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV295" s="5"/>
+      <c r="AW295" s="5"/>
+    </row>
+    <row r="296" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C296" s="5"/>
       <c r="D296" s="5"/>
       <c r="E296" s="5"/>
@@ -16944,8 +17646,10 @@
       <c r="AS296" s="5"/>
       <c r="AT296" s="5"/>
       <c r="AU296" s="5"/>
-    </row>
-    <row r="297" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV296" s="5"/>
+      <c r="AW296" s="5"/>
+    </row>
+    <row r="297" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C297" s="5"/>
       <c r="D297" s="5"/>
       <c r="E297" s="5"/>
@@ -16991,8 +17695,10 @@
       <c r="AS297" s="5"/>
       <c r="AT297" s="5"/>
       <c r="AU297" s="5"/>
-    </row>
-    <row r="298" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV297" s="5"/>
+      <c r="AW297" s="5"/>
+    </row>
+    <row r="298" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C298" s="5"/>
       <c r="D298" s="5"/>
       <c r="E298" s="5"/>
@@ -17038,8 +17744,10 @@
       <c r="AS298" s="5"/>
       <c r="AT298" s="5"/>
       <c r="AU298" s="5"/>
-    </row>
-    <row r="299" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV298" s="5"/>
+      <c r="AW298" s="5"/>
+    </row>
+    <row r="299" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C299" s="5"/>
       <c r="D299" s="5"/>
       <c r="E299" s="5"/>
@@ -17085,8 +17793,10 @@
       <c r="AS299" s="5"/>
       <c r="AT299" s="5"/>
       <c r="AU299" s="5"/>
-    </row>
-    <row r="300" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV299" s="5"/>
+      <c r="AW299" s="5"/>
+    </row>
+    <row r="300" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C300" s="5"/>
       <c r="D300" s="5"/>
       <c r="E300" s="5"/>
@@ -17132,8 +17842,10 @@
       <c r="AS300" s="5"/>
       <c r="AT300" s="5"/>
       <c r="AU300" s="5"/>
-    </row>
-    <row r="301" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV300" s="5"/>
+      <c r="AW300" s="5"/>
+    </row>
+    <row r="301" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C301" s="5"/>
       <c r="D301" s="5"/>
       <c r="E301" s="5"/>
@@ -17179,8 +17891,10 @@
       <c r="AS301" s="5"/>
       <c r="AT301" s="5"/>
       <c r="AU301" s="5"/>
-    </row>
-    <row r="302" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV301" s="5"/>
+      <c r="AW301" s="5"/>
+    </row>
+    <row r="302" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C302" s="5"/>
       <c r="D302" s="5"/>
       <c r="E302" s="5"/>
@@ -17226,8 +17940,10 @@
       <c r="AS302" s="5"/>
       <c r="AT302" s="5"/>
       <c r="AU302" s="5"/>
-    </row>
-    <row r="303" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV302" s="5"/>
+      <c r="AW302" s="5"/>
+    </row>
+    <row r="303" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C303" s="5"/>
       <c r="D303" s="5"/>
       <c r="E303" s="5"/>
@@ -17273,8 +17989,10 @@
       <c r="AS303" s="5"/>
       <c r="AT303" s="5"/>
       <c r="AU303" s="5"/>
-    </row>
-    <row r="304" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV303" s="5"/>
+      <c r="AW303" s="5"/>
+    </row>
+    <row r="304" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C304" s="5"/>
       <c r="D304" s="5"/>
       <c r="E304" s="5"/>
@@ -17320,8 +18038,10 @@
       <c r="AS304" s="5"/>
       <c r="AT304" s="5"/>
       <c r="AU304" s="5"/>
-    </row>
-    <row r="305" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV304" s="5"/>
+      <c r="AW304" s="5"/>
+    </row>
+    <row r="305" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C305" s="5"/>
       <c r="D305" s="5"/>
       <c r="E305" s="5"/>
@@ -17367,8 +18087,10 @@
       <c r="AS305" s="5"/>
       <c r="AT305" s="5"/>
       <c r="AU305" s="5"/>
-    </row>
-    <row r="306" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV305" s="5"/>
+      <c r="AW305" s="5"/>
+    </row>
+    <row r="306" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C306" s="5"/>
       <c r="D306" s="5"/>
       <c r="E306" s="5"/>
@@ -17414,8 +18136,10 @@
       <c r="AS306" s="5"/>
       <c r="AT306" s="5"/>
       <c r="AU306" s="5"/>
-    </row>
-    <row r="307" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV306" s="5"/>
+      <c r="AW306" s="5"/>
+    </row>
+    <row r="307" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C307" s="5"/>
       <c r="D307" s="5"/>
       <c r="E307" s="5"/>
@@ -17461,8 +18185,10 @@
       <c r="AS307" s="5"/>
       <c r="AT307" s="5"/>
       <c r="AU307" s="5"/>
-    </row>
-    <row r="308" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV307" s="5"/>
+      <c r="AW307" s="5"/>
+    </row>
+    <row r="308" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C308" s="5"/>
       <c r="D308" s="5"/>
       <c r="E308" s="5"/>
@@ -17508,8 +18234,10 @@
       <c r="AS308" s="5"/>
       <c r="AT308" s="5"/>
       <c r="AU308" s="5"/>
-    </row>
-    <row r="309" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV308" s="5"/>
+      <c r="AW308" s="5"/>
+    </row>
+    <row r="309" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C309" s="5"/>
       <c r="D309" s="5"/>
       <c r="E309" s="5"/>
@@ -17555,8 +18283,10 @@
       <c r="AS309" s="5"/>
       <c r="AT309" s="5"/>
       <c r="AU309" s="5"/>
-    </row>
-    <row r="310" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV309" s="5"/>
+      <c r="AW309" s="5"/>
+    </row>
+    <row r="310" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C310" s="5"/>
       <c r="D310" s="5"/>
       <c r="E310" s="5"/>
@@ -17602,8 +18332,10 @@
       <c r="AS310" s="5"/>
       <c r="AT310" s="5"/>
       <c r="AU310" s="5"/>
-    </row>
-    <row r="311" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV310" s="5"/>
+      <c r="AW310" s="5"/>
+    </row>
+    <row r="311" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C311" s="5"/>
       <c r="D311" s="5"/>
       <c r="E311" s="5"/>
@@ -17649,8 +18381,10 @@
       <c r="AS311" s="5"/>
       <c r="AT311" s="5"/>
       <c r="AU311" s="5"/>
-    </row>
-    <row r="312" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV311" s="5"/>
+      <c r="AW311" s="5"/>
+    </row>
+    <row r="312" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C312" s="5"/>
       <c r="D312" s="5"/>
       <c r="E312" s="5"/>
@@ -17696,8 +18430,10 @@
       <c r="AS312" s="5"/>
       <c r="AT312" s="5"/>
       <c r="AU312" s="5"/>
-    </row>
-    <row r="313" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV312" s="5"/>
+      <c r="AW312" s="5"/>
+    </row>
+    <row r="313" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C313" s="5"/>
       <c r="D313" s="5"/>
       <c r="E313" s="5"/>
@@ -17743,8 +18479,10 @@
       <c r="AS313" s="5"/>
       <c r="AT313" s="5"/>
       <c r="AU313" s="5"/>
-    </row>
-    <row r="314" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV313" s="5"/>
+      <c r="AW313" s="5"/>
+    </row>
+    <row r="314" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C314" s="5"/>
       <c r="D314" s="5"/>
       <c r="E314" s="5"/>
@@ -17790,8 +18528,10 @@
       <c r="AS314" s="5"/>
       <c r="AT314" s="5"/>
       <c r="AU314" s="5"/>
-    </row>
-    <row r="315" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV314" s="5"/>
+      <c r="AW314" s="5"/>
+    </row>
+    <row r="315" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C315" s="5"/>
       <c r="D315" s="5"/>
       <c r="E315" s="5"/>
@@ -17837,8 +18577,10 @@
       <c r="AS315" s="5"/>
       <c r="AT315" s="5"/>
       <c r="AU315" s="5"/>
-    </row>
-    <row r="316" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV315" s="5"/>
+      <c r="AW315" s="5"/>
+    </row>
+    <row r="316" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C316" s="5"/>
       <c r="D316" s="5"/>
       <c r="E316" s="5"/>
@@ -17884,8 +18626,10 @@
       <c r="AS316" s="5"/>
       <c r="AT316" s="5"/>
       <c r="AU316" s="5"/>
-    </row>
-    <row r="317" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV316" s="5"/>
+      <c r="AW316" s="5"/>
+    </row>
+    <row r="317" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C317" s="5"/>
       <c r="D317" s="5"/>
       <c r="E317" s="5"/>
@@ -17931,8 +18675,10 @@
       <c r="AS317" s="5"/>
       <c r="AT317" s="5"/>
       <c r="AU317" s="5"/>
-    </row>
-    <row r="318" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV317" s="5"/>
+      <c r="AW317" s="5"/>
+    </row>
+    <row r="318" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C318" s="5"/>
       <c r="D318" s="5"/>
       <c r="E318" s="5"/>
@@ -17978,8 +18724,10 @@
       <c r="AS318" s="5"/>
       <c r="AT318" s="5"/>
       <c r="AU318" s="5"/>
-    </row>
-    <row r="319" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV318" s="5"/>
+      <c r="AW318" s="5"/>
+    </row>
+    <row r="319" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C319" s="5"/>
       <c r="D319" s="5"/>
       <c r="E319" s="5"/>
@@ -18025,8 +18773,10 @@
       <c r="AS319" s="5"/>
       <c r="AT319" s="5"/>
       <c r="AU319" s="5"/>
-    </row>
-    <row r="320" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV319" s="5"/>
+      <c r="AW319" s="5"/>
+    </row>
+    <row r="320" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C320" s="5"/>
       <c r="D320" s="5"/>
       <c r="E320" s="5"/>
@@ -18072,8 +18822,10 @@
       <c r="AS320" s="5"/>
       <c r="AT320" s="5"/>
       <c r="AU320" s="5"/>
-    </row>
-    <row r="321" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV320" s="5"/>
+      <c r="AW320" s="5"/>
+    </row>
+    <row r="321" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C321" s="5"/>
       <c r="D321" s="5"/>
       <c r="E321" s="5"/>
@@ -18119,8 +18871,10 @@
       <c r="AS321" s="5"/>
       <c r="AT321" s="5"/>
       <c r="AU321" s="5"/>
-    </row>
-    <row r="322" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV321" s="5"/>
+      <c r="AW321" s="5"/>
+    </row>
+    <row r="322" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C322" s="5"/>
       <c r="D322" s="5"/>
       <c r="E322" s="5"/>
@@ -18166,8 +18920,10 @@
       <c r="AS322" s="5"/>
       <c r="AT322" s="5"/>
       <c r="AU322" s="5"/>
-    </row>
-    <row r="323" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV322" s="5"/>
+      <c r="AW322" s="5"/>
+    </row>
+    <row r="323" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C323" s="5"/>
       <c r="D323" s="5"/>
       <c r="E323" s="5"/>
@@ -18213,8 +18969,10 @@
       <c r="AS323" s="5"/>
       <c r="AT323" s="5"/>
       <c r="AU323" s="5"/>
-    </row>
-    <row r="324" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV323" s="5"/>
+      <c r="AW323" s="5"/>
+    </row>
+    <row r="324" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C324" s="5"/>
       <c r="D324" s="5"/>
       <c r="E324" s="5"/>
@@ -18260,8 +19018,10 @@
       <c r="AS324" s="5"/>
       <c r="AT324" s="5"/>
       <c r="AU324" s="5"/>
-    </row>
-    <row r="325" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV324" s="5"/>
+      <c r="AW324" s="5"/>
+    </row>
+    <row r="325" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C325" s="5"/>
       <c r="D325" s="5"/>
       <c r="E325" s="5"/>
@@ -18307,8 +19067,10 @@
       <c r="AS325" s="5"/>
       <c r="AT325" s="5"/>
       <c r="AU325" s="5"/>
-    </row>
-    <row r="326" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV325" s="5"/>
+      <c r="AW325" s="5"/>
+    </row>
+    <row r="326" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C326" s="5"/>
       <c r="D326" s="5"/>
       <c r="E326" s="5"/>
@@ -18354,8 +19116,10 @@
       <c r="AS326" s="5"/>
       <c r="AT326" s="5"/>
       <c r="AU326" s="5"/>
-    </row>
-    <row r="327" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV326" s="5"/>
+      <c r="AW326" s="5"/>
+    </row>
+    <row r="327" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C327" s="5"/>
       <c r="D327" s="5"/>
       <c r="E327" s="5"/>
@@ -18401,8 +19165,10 @@
       <c r="AS327" s="5"/>
       <c r="AT327" s="5"/>
       <c r="AU327" s="5"/>
-    </row>
-    <row r="328" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV327" s="5"/>
+      <c r="AW327" s="5"/>
+    </row>
+    <row r="328" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C328" s="5"/>
       <c r="D328" s="5"/>
       <c r="E328" s="5"/>
@@ -18448,8 +19214,10 @@
       <c r="AS328" s="5"/>
       <c r="AT328" s="5"/>
       <c r="AU328" s="5"/>
-    </row>
-    <row r="329" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV328" s="5"/>
+      <c r="AW328" s="5"/>
+    </row>
+    <row r="329" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C329" s="5"/>
       <c r="D329" s="5"/>
       <c r="E329" s="5"/>
@@ -18495,8 +19263,10 @@
       <c r="AS329" s="5"/>
       <c r="AT329" s="5"/>
       <c r="AU329" s="5"/>
-    </row>
-    <row r="330" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV329" s="5"/>
+      <c r="AW329" s="5"/>
+    </row>
+    <row r="330" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C330" s="5"/>
       <c r="D330" s="5"/>
       <c r="E330" s="5"/>
@@ -18542,8 +19312,10 @@
       <c r="AS330" s="5"/>
       <c r="AT330" s="5"/>
       <c r="AU330" s="5"/>
-    </row>
-    <row r="331" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV330" s="5"/>
+      <c r="AW330" s="5"/>
+    </row>
+    <row r="331" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C331" s="5"/>
       <c r="D331" s="5"/>
       <c r="E331" s="5"/>
@@ -18589,8 +19361,10 @@
       <c r="AS331" s="5"/>
       <c r="AT331" s="5"/>
       <c r="AU331" s="5"/>
-    </row>
-    <row r="332" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV331" s="5"/>
+      <c r="AW331" s="5"/>
+    </row>
+    <row r="332" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C332" s="5"/>
       <c r="D332" s="5"/>
       <c r="E332" s="5"/>
@@ -18636,8 +19410,10 @@
       <c r="AS332" s="5"/>
       <c r="AT332" s="5"/>
       <c r="AU332" s="5"/>
-    </row>
-    <row r="333" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV332" s="5"/>
+      <c r="AW332" s="5"/>
+    </row>
+    <row r="333" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C333" s="5"/>
       <c r="D333" s="5"/>
       <c r="E333" s="5"/>
@@ -18683,8 +19459,10 @@
       <c r="AS333" s="5"/>
       <c r="AT333" s="5"/>
       <c r="AU333" s="5"/>
-    </row>
-    <row r="334" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV333" s="5"/>
+      <c r="AW333" s="5"/>
+    </row>
+    <row r="334" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C334" s="5"/>
       <c r="D334" s="5"/>
       <c r="E334" s="5"/>
@@ -18730,8 +19508,10 @@
       <c r="AS334" s="5"/>
       <c r="AT334" s="5"/>
       <c r="AU334" s="5"/>
-    </row>
-    <row r="335" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV334" s="5"/>
+      <c r="AW334" s="5"/>
+    </row>
+    <row r="335" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C335" s="5"/>
       <c r="D335" s="5"/>
       <c r="E335" s="5"/>
@@ -18777,8 +19557,10 @@
       <c r="AS335" s="5"/>
       <c r="AT335" s="5"/>
       <c r="AU335" s="5"/>
-    </row>
-    <row r="336" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV335" s="5"/>
+      <c r="AW335" s="5"/>
+    </row>
+    <row r="336" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C336" s="5"/>
       <c r="D336" s="5"/>
       <c r="E336" s="5"/>
@@ -18824,8 +19606,10 @@
       <c r="AS336" s="5"/>
       <c r="AT336" s="5"/>
       <c r="AU336" s="5"/>
-    </row>
-    <row r="337" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV336" s="5"/>
+      <c r="AW336" s="5"/>
+    </row>
+    <row r="337" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C337" s="5"/>
       <c r="D337" s="5"/>
       <c r="E337" s="5"/>
@@ -18871,8 +19655,10 @@
       <c r="AS337" s="5"/>
       <c r="AT337" s="5"/>
       <c r="AU337" s="5"/>
-    </row>
-    <row r="338" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV337" s="5"/>
+      <c r="AW337" s="5"/>
+    </row>
+    <row r="338" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C338" s="5"/>
       <c r="D338" s="5"/>
       <c r="E338" s="5"/>
@@ -18918,8 +19704,10 @@
       <c r="AS338" s="5"/>
       <c r="AT338" s="5"/>
       <c r="AU338" s="5"/>
-    </row>
-    <row r="339" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV338" s="5"/>
+      <c r="AW338" s="5"/>
+    </row>
+    <row r="339" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C339" s="5"/>
       <c r="D339" s="5"/>
       <c r="E339" s="5"/>
@@ -18965,8 +19753,10 @@
       <c r="AS339" s="5"/>
       <c r="AT339" s="5"/>
       <c r="AU339" s="5"/>
-    </row>
-    <row r="340" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV339" s="5"/>
+      <c r="AW339" s="5"/>
+    </row>
+    <row r="340" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C340" s="5"/>
       <c r="D340" s="5"/>
       <c r="E340" s="5"/>
@@ -19012,8 +19802,10 @@
       <c r="AS340" s="5"/>
       <c r="AT340" s="5"/>
       <c r="AU340" s="5"/>
-    </row>
-    <row r="341" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV340" s="5"/>
+      <c r="AW340" s="5"/>
+    </row>
+    <row r="341" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C341" s="5"/>
       <c r="D341" s="5"/>
       <c r="E341" s="5"/>
@@ -19059,8 +19851,10 @@
       <c r="AS341" s="5"/>
       <c r="AT341" s="5"/>
       <c r="AU341" s="5"/>
-    </row>
-    <row r="342" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV341" s="5"/>
+      <c r="AW341" s="5"/>
+    </row>
+    <row r="342" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C342" s="5"/>
       <c r="D342" s="5"/>
       <c r="E342" s="5"/>
@@ -19106,8 +19900,10 @@
       <c r="AS342" s="5"/>
       <c r="AT342" s="5"/>
       <c r="AU342" s="5"/>
-    </row>
-    <row r="343" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV342" s="5"/>
+      <c r="AW342" s="5"/>
+    </row>
+    <row r="343" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C343" s="5"/>
       <c r="D343" s="5"/>
       <c r="E343" s="5"/>
@@ -19153,8 +19949,10 @@
       <c r="AS343" s="5"/>
       <c r="AT343" s="5"/>
       <c r="AU343" s="5"/>
-    </row>
-    <row r="344" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV343" s="5"/>
+      <c r="AW343" s="5"/>
+    </row>
+    <row r="344" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C344" s="5"/>
       <c r="D344" s="5"/>
       <c r="E344" s="5"/>
@@ -19200,8 +19998,10 @@
       <c r="AS344" s="5"/>
       <c r="AT344" s="5"/>
       <c r="AU344" s="5"/>
-    </row>
-    <row r="345" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV344" s="5"/>
+      <c r="AW344" s="5"/>
+    </row>
+    <row r="345" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C345" s="5"/>
       <c r="D345" s="5"/>
       <c r="E345" s="5"/>
@@ -19247,8 +20047,10 @@
       <c r="AS345" s="5"/>
       <c r="AT345" s="5"/>
       <c r="AU345" s="5"/>
-    </row>
-    <row r="346" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV345" s="5"/>
+      <c r="AW345" s="5"/>
+    </row>
+    <row r="346" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C346" s="5"/>
       <c r="D346" s="5"/>
       <c r="E346" s="5"/>
@@ -19294,8 +20096,10 @@
       <c r="AS346" s="5"/>
       <c r="AT346" s="5"/>
       <c r="AU346" s="5"/>
-    </row>
-    <row r="347" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV346" s="5"/>
+      <c r="AW346" s="5"/>
+    </row>
+    <row r="347" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C347" s="5"/>
       <c r="D347" s="5"/>
       <c r="E347" s="5"/>
@@ -19341,8 +20145,10 @@
       <c r="AS347" s="5"/>
       <c r="AT347" s="5"/>
       <c r="AU347" s="5"/>
-    </row>
-    <row r="348" spans="3:47" x14ac:dyDescent="0.2">
+      <c r="AV347" s="5"/>
+      <c r="AW347" s="5"/>
+    </row>
+    <row r="348" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C348" s="5"/>
       <c r="D348" s="5"/>
       <c r="E348" s="5"/>
@@ -19388,6 +20194,8 @@
       <c r="AS348" s="5"/>
       <c r="AT348" s="5"/>
       <c r="AU348" s="5"/>
+      <c r="AV348" s="5"/>
+      <c r="AW348" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
